--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -21,10 +21,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26-05 (Rayimova.X)'!$A$1:$X$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26-06 (Yuldashev.O)'!$A$1:$X$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Safdan chiqarilganlar'!$A$1:$X$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44752,7 +44752,7 @@
       </c>
       <c r="B477" s="8" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C477" s="9" t="inlineStr">
@@ -62316,7 +62316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -64844,76 +64844,70 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr"/>
+          <t>Ulugbekova Zara</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>46272</v>
-      </c>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Dalerovna</t>
+          <t>Ulug'bek qizi</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
-        </is>
-      </c>
+          <t>Ulugbekova Zara Ulug'bek qizi</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>AE4114421</t>
+          <t>AE4760779</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>60508095680049</t>
+          <t>61109085590127</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>09.09.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>05.08.2009</t>
+          <t>11.09.2008</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
-          <t>Tuychiyeva Farzona Dalerovna</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P23" s="8" t="inlineStr">
         <is>
-          <t>UM-O 00064269</t>
-        </is>
-      </c>
-      <c r="Q23" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03728161</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr"/>
       <c r="R23" s="10" t="inlineStr">
         <is>
-          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S23" s="11" t="inlineStr">
@@ -64923,24 +64917,12 @@
       </c>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V23" s="10" t="inlineStr">
-        <is>
-          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
-        </is>
-      </c>
-      <c r="W23" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U23" s="11" t="inlineStr"/>
+      <c r="V23" s="10" t="inlineStr"/>
+      <c r="W23" s="6" t="inlineStr"/>
       <c r="X23" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -64958,7 +64940,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara</t>
+          <t>Xamdamova Madina</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -64968,75 +64950,94 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>46197</v>
+      </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Ulug'bek qizi</t>
+          <t>Abdiqodir qizi</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Ulugbekova Zara Ulug'bek qizi</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr"/>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>AE4760779</t>
+          <t>AB8517012</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61109085590127</t>
+          <t>62701015680026</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>07.01.2018</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>11.09.2008</t>
+          <t>27.01.2001</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xamdamova Madina Abdiqodir qizi</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>UM 03728161</t>
+          <t>K 5487959</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>5-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Diplom</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="inlineStr"/>
-      <c r="V24" s="4" t="inlineStr"/>
-      <c r="W24" s="6" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
+to'g'risi: 62701015680026</t>
+        </is>
+      </c>
+      <c r="W24" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X24" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -65054,55 +65055,51 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Xamdamova Madina</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xannonova Shohsanam</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>181</t>
         </is>
       </c>
       <c r="F25" s="18" t="n">
-        <v>46197</v>
+        <v>46247</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Abdiqodir qizi</t>
+          <t>Orif qizi</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
+          <t>Xannonova Shohsanam Orif qizi</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>AB8517012</t>
+          <t>AD0284895</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>62701015680026</t>
+          <t>60206045680052</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>07.01.2018</t>
+          <t>01.04.2021</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>27.01.2001</t>
+          <t>02.06.2004</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
@@ -65110,46 +65107,33 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O25" s="10" t="inlineStr">
-        <is>
-          <t>Xamdamova Madina Abdiqodir qizi</t>
-        </is>
-      </c>
+      <c r="O25" s="10" t="inlineStr"/>
       <c r="P25" s="8" t="inlineStr">
         <is>
-          <t>K 5487959</t>
+          <t>UM 0862565</t>
         </is>
       </c>
       <c r="Q25" s="10" t="inlineStr"/>
       <c r="R25" s="10" t="inlineStr">
         <is>
-          <t>Kitob qishloq xo‘jalik kasb-hunar kolleji</t>
-        </is>
-      </c>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>Diplom</t>
-        </is>
-      </c>
+          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
+        </is>
+      </c>
+      <c r="S25" s="11" t="inlineStr"/>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V25" s="10" t="inlineStr">
-        <is>
-          <t>Operator: faqat 42701015680026 jshshr xato yozilibdi
-to'g'risi: 62701015680026</t>
-        </is>
-      </c>
-      <c r="W25" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U25" s="15" t="inlineStr">
+        <is>
+          <t>CHALA</t>
+        </is>
+      </c>
+      <c r="V25" s="10" t="inlineStr"/>
+      <c r="W25" s="16" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
         </is>
       </c>
       <c r="X25" s="7" t="inlineStr">
@@ -65169,51 +65153,57 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>Xo'jaqulova Navbahor</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>46247</v>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Orif qizi</t>
+          <t>Azim qizi</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Xannonova Shohsanam Orif qizi</t>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>AD0284895</t>
+          <t>AD4186543</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>60206045680052</t>
+          <t>62104025680040</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>01.04.2021</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>02.06.2004</t>
+          <t>21.04.2002</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -65221,33 +65211,43 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>UM 0862565</t>
+          <t>UM 0086260</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>1-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktab</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U26" s="15" t="inlineStr">
-        <is>
-          <t>CHALA</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="inlineStr"/>
-      <c r="W26" s="16" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
+          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
+        </is>
+      </c>
+      <c r="W26" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X26" s="7" t="inlineStr">
@@ -65267,7 +65267,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor</t>
+          <t>Xolmurodova Dilnura</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -65277,68 +65277,72 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>2026-09-14 00:00:00</t>
+          <t>2026-09-15 00:00:00</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Azim qizi</t>
+          <t>Dilmurod qizi</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>AD4186543</t>
+          <t>AE1516812</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>62104025680040</t>
+          <t>60110085590193</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>21.04.2002</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O27" s="10" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="P27" s="8" t="inlineStr">
         <is>
-          <t>UM 0086260</t>
-        </is>
-      </c>
-      <c r="Q27" s="10" t="inlineStr"/>
+          <t>UM 03755333</t>
+        </is>
+      </c>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
+        </is>
+      </c>
       <c r="R27" s="10" t="inlineStr">
         <is>
-          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S27" s="11" t="inlineStr">
@@ -65347,7 +65351,7 @@
         </is>
       </c>
       <c r="T27" s="11" t="n">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="U27" s="7" t="inlineStr">
         <is>
@@ -65356,7 +65360,7 @@
       </c>
       <c r="V27" s="10" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
         </is>
       </c>
       <c r="W27" s="13" t="inlineStr">
@@ -65381,7 +65385,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura</t>
+          <t>Xujamuratova Durdona</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -65391,72 +65395,60 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-15 00:00:00</t>
-        </is>
-      </c>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Dilmurod qizi</t>
+          <t>Bahrom qizi</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
-        </is>
-      </c>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>AE1516812</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>60110085590193</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>22.04.2008</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>UM 03755333</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03717652</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -65464,24 +65456,14 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T28" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W28" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr"/>
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="6" t="inlineStr"/>
       <c r="X28" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -65499,7 +65481,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona</t>
+          <t>Xurramova Shahnoza</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -65509,75 +65491,89 @@
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr"/>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>46204</v>
+      </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Bahrom qizi</t>
+          <t>Shuhrat qizi</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr"/>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
+        </is>
+      </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>AE5954513</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>62204085720105</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>22.04.2008</t>
+          <t>04.11.2001</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="P29" s="8" t="inlineStr">
         <is>
-          <t>UM 03717652</t>
+          <t>UM 0084478</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr"/>
       <c r="R29" s="10" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S29" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Attestat</t>
         </is>
       </c>
       <c r="T29" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="U29" s="11" t="inlineStr"/>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V29" s="10" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
+      <c r="W29" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X29" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -65595,7 +65591,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza</t>
+          <t>Xurramova Shahrizoda</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -65605,11 +65601,13 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>46204</v>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
@@ -65618,32 +65616,32 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
+          <t>30.04.2007</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -65653,28 +65651,32 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>UM 0084478</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr"/>
+          <t>UM 02149677</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
+        </is>
+      </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>Attestat</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T30" s="5" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U30" s="7" t="inlineStr">
@@ -65705,7 +65707,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda</t>
+          <t>Xusanova Aziza</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -65715,7 +65717,7 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -65725,62 +65727,62 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Shuhrat qizi</t>
+          <t>Fazliddin qizi</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O31" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xusanova Aziza Fazliddin qizi</t>
         </is>
       </c>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>UM 02149677</t>
+          <t>UM 03753649</t>
         </is>
       </c>
       <c r="Q31" s="10" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
         </is>
       </c>
       <c r="R31" s="10" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="11" t="inlineStr">
@@ -65790,7 +65792,7 @@
       </c>
       <c r="T31" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U31" s="7" t="inlineStr">
@@ -65798,10 +65800,14 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V31" s="10" t="inlineStr"/>
+      <c r="V31" s="10" t="inlineStr">
+        <is>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+        </is>
+      </c>
       <c r="W31" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X31" s="7" t="inlineStr">
@@ -65821,7 +65827,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza</t>
+          <t>Zayidova Shaboda</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -65831,7 +65837,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -65841,62 +65847,62 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Fazliddin qizi</t>
+          <t>Sodiqovna</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>31.12.2008</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
+          <t>Zayidova Shaboda Sodiqovna</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 03753649</t>
+          <t>UM 03729571</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
         </is>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
@@ -65914,14 +65920,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
-        </is>
-      </c>
+      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="13" t="inlineStr">
         <is>
-          <t>Shahodatnoma: MOS</t>
+          <t>Pasport: MOS</t>
         </is>
       </c>
       <c r="X32" s="7" t="inlineStr">
@@ -65930,124 +65932,8 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>26-04</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Zayidova Shaboda</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>Sodiqovna</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>AE5856503</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>63112085680039</t>
-        </is>
-      </c>
-      <c r="L33" s="11" t="inlineStr">
-        <is>
-          <t>14.01.2026</t>
-        </is>
-      </c>
-      <c r="M33" s="11" t="inlineStr">
-        <is>
-          <t>31.12.2008</t>
-        </is>
-      </c>
-      <c r="N33" s="11" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O33" s="10" t="inlineStr">
-        <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t>UM 03729571</t>
-        </is>
-      </c>
-      <c r="Q33" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
-        </is>
-      </c>
-      <c r="R33" s="10" t="inlineStr">
-        <is>
-          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
-        </is>
-      </c>
-      <c r="S33" s="11" t="inlineStr">
-        <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T33" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U33" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V33" s="10" t="inlineStr"/>
-      <c r="W33" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
-      <c r="X33" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X33"/>
+  <autoFilter ref="A1:X32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -73770,7 +73656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -76248,73 +76134,103 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Uktamova Sarvinoz</t>
+          <t>Tuychiyeva Farzona</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="11" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>46272</v>
+      </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Obid qizi</t>
+          <t>Dalerovna</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>Uktamova Sarvinoz Obid qizi</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr"/>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>AB6325652</t>
+          <t>AE4114421</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>61901005590031</t>
+          <t>60508095680049</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>29.03.2017</t>
+          <t>09.09.2025</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>19.01.2000</t>
+          <t>05.08.2009</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O31" s="10" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>Tuychiyeva Farzona Dalerovna</t>
+        </is>
+      </c>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t>K 5050490</t>
-        </is>
-      </c>
-      <c r="Q31" s="10" t="inlineStr"/>
+          <t>UM-O 00064269</t>
+        </is>
+      </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3884713/3404183/e0f02e0b-2135-4684-83d1-f3e60ea32b99?preview=true</t>
+        </is>
+      </c>
       <c r="R31" s="10" t="inlineStr">
         <is>
-          <t>Shahrisabz iqtisodiyot kolleji</t>
+          <t>34-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S31" s="11" t="inlineStr">
         <is>
-          <t>Kollej</t>
-        </is>
-      </c>
-      <c r="T31" s="11" t="inlineStr"/>
-      <c r="U31" s="11" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V31" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
-        </is>
-      </c>
-      <c r="W31" s="6" t="inlineStr"/>
+          <t>ID-karta AE4114421 va Shahodatnoma UM 00064269 bo'yicha to'liq tasdiqlandi (#280)</t>
+        </is>
+      </c>
+      <c r="W31" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X31" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -76332,7 +76248,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Usmonova Jasmina</t>
+          <t>Uktamova Sarvinoz</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
@@ -76340,33 +76256,33 @@
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Nodir qizi</t>
+          <t>Obid qizi</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Usmonova Jasmina Nodir qizi</t>
+          <t>Uktamova Sarvinoz Obid qizi</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>AD9134105</t>
+          <t>AB6325652</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>62712075590017</t>
+          <t>61901005590031</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>24.10.2024</t>
+          <t>29.03.2017</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>27.12.2007</t>
+          <t>19.01.2000</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
@@ -76377,25 +76293,25 @@
       <c r="O32" s="4" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>UM 03298099</t>
+          <t>K 5050490</t>
         </is>
       </c>
       <c r="Q32" s="4" t="inlineStr"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>45-maktab</t>
+          <t>Shahrisabz iqtisodiyot kolleji</t>
         </is>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr"/>
       <c r="U32" s="5" t="inlineStr"/>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
+          <t>2025-2026 kontingenti: 2-kurs</t>
         </is>
       </c>
       <c r="W32" s="6" t="inlineStr"/>
@@ -76416,7 +76332,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Usmonova Shabbona</t>
+          <t>Usmonova Jasmina</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr"/>
@@ -76424,33 +76340,33 @@
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Botir qizi</t>
+          <t>Nodir qizi</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Usmonova Shabbona Botir qizi</t>
+          <t>Usmonova Jasmina Nodir qizi</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>AD9713077</t>
+          <t>AD9134105</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>61412075590059</t>
+          <t>62712075590017</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>06.12.2024</t>
+          <t>24.10.2024</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>14.12.2007</t>
+          <t>27.12.2007</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
@@ -76461,13 +76377,13 @@
       <c r="O33" s="10" t="inlineStr"/>
       <c r="P33" s="8" t="inlineStr">
         <is>
-          <t>UM 03295752</t>
+          <t>UM 03298099</t>
         </is>
       </c>
       <c r="Q33" s="10" t="inlineStr"/>
       <c r="R33" s="10" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>45-maktab</t>
         </is>
       </c>
       <c r="S33" s="11" t="inlineStr">
@@ -76479,7 +76395,7 @@
       <c r="U33" s="11" t="inlineStr"/>
       <c r="V33" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-17</t>
         </is>
       </c>
       <c r="W33" s="6" t="inlineStr"/>
@@ -76500,49 +76416,41 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Usmonova Shabbona</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Nurali qizi</t>
+          <t>Botir qizi</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
-        </is>
-      </c>
+          <t>Usmonova Shabbona Botir qizi</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>AE 4385291</t>
+          <t>AD9713077</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>407129 0256 0079</t>
+          <t>61412075590059</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>29.09.2025</t>
+          <t>06.12.2024</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>14.12.2007</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -76553,31 +76461,27 @@
       <c r="O34" s="4" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>O'R-A 5263487</t>
+          <t>UM 03295752</t>
         </is>
       </c>
       <c r="Q34" s="4" t="inlineStr"/>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-maktab</t>
         </is>
       </c>
       <c r="S34" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="U34" s="15" t="inlineStr">
-        <is>
-          <t>Chala</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="inlineStr"/>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
       <c r="W34" s="6" t="inlineStr"/>
       <c r="X34" s="7" t="inlineStr">
         <is>
@@ -76596,39 +76500,51 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Xamrayeva Niginabonu</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr"/>
+          <t>Uzoqova Fazilat</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E35" s="11" t="inlineStr"/>
       <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Jamshid qizi</t>
+          <t>Nurali qizi</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Xamrayeva Niginabonu Jamshid qizi</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr"/>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Uzoqova Fazilat Nurali qizi</t>
+        </is>
+      </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>AD9506052</t>
+          <t>AE 4385291</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>61508075590121</t>
+          <t>407129 0256 0079</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>21,11,2024</t>
-        </is>
-      </c>
-      <c r="M35" s="11" t="inlineStr"/>
+          <t>29.09.2025</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>07.12.1990</t>
+        </is>
+      </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
@@ -76637,27 +76553,31 @@
       <c r="O35" s="10" t="inlineStr"/>
       <c r="P35" s="8" t="inlineStr">
         <is>
-          <t>UM 03295886</t>
+          <t>O'R-A 5263487</t>
         </is>
       </c>
       <c r="Q35" s="10" t="inlineStr"/>
       <c r="R35" s="10" t="inlineStr">
         <is>
-          <t>10-maktab</t>
+          <t>8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S35" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T35" s="11" t="inlineStr"/>
-      <c r="U35" s="11" t="inlineStr"/>
-      <c r="V35" s="10" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
-        </is>
-      </c>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U35" s="15" t="inlineStr">
+        <is>
+          <t>Chala</t>
+        </is>
+      </c>
+      <c r="V35" s="10" t="inlineStr"/>
       <c r="W35" s="6" t="inlineStr"/>
       <c r="X35" s="7" t="inlineStr">
         <is>
@@ -76676,7 +76596,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna</t>
+          <t>Xamrayeva Niginabonu</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr"/>
@@ -76684,28 +76604,28 @@
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Hushvaqt qizi</t>
+          <t>Jamshid qizi</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna Hushvaqt qizi</t>
+          <t>Xamrayeva Niginabonu Jamshid qizi</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>AE2747402</t>
+          <t>AD9506052</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>40312902560107</t>
+          <t>61508075590121</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>20,05,2025</t>
+          <t>21,11,2024</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr"/>
@@ -76717,18 +76637,18 @@
       <c r="O36" s="4" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>K 1234480</t>
+          <t>UM 03295886</t>
         </is>
       </c>
       <c r="Q36" s="4" t="inlineStr"/>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>Miroqi sport pedagogika kolleji</t>
+          <t>10-maktab</t>
         </is>
       </c>
       <c r="S36" s="5" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T36" s="5" t="inlineStr"/>
@@ -76756,7 +76676,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda</t>
+          <t>Yoqubova Maftuna</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr"/>
@@ -76764,28 +76684,28 @@
       <c r="F37" s="11" t="inlineStr"/>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Hasanovna</t>
+          <t>Hushvaqt qizi</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda Hasanovna</t>
+          <t>Yoqubova Maftuna Hushvaqt qizi</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr"/>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>AB7535578</t>
+          <t>AE2747402</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>40108945590034</t>
+          <t>40312902560107</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>22,08,2017</t>
+          <t>20,05,2025</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr"/>
@@ -76797,13 +76717,13 @@
       <c r="O37" s="10" t="inlineStr"/>
       <c r="P37" s="8" t="inlineStr">
         <is>
-          <t>K 2404534</t>
+          <t>K 1234480</t>
         </is>
       </c>
       <c r="Q37" s="10" t="inlineStr"/>
       <c r="R37" s="10" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika kolleji</t>
+          <t>Miroqi sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S37" s="11" t="inlineStr">
@@ -76836,7 +76756,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro</t>
+          <t>Yuldosheva Iroda</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr"/>
@@ -76844,28 +76764,28 @@
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Ubaydullo qizi</t>
+          <t>Hasanovna</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+          <t>Yuldosheva Iroda Hasanovna</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>AD8888020</t>
+          <t>AB7535578</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>62609075590027</t>
+          <t>40108945590034</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>07,10,2024</t>
+          <t>22,08,2017</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr"/>
@@ -76877,18 +76797,18 @@
       <c r="O38" s="4" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>UM 03295463</t>
+          <t>K 2404534</t>
         </is>
       </c>
       <c r="Q38" s="4" t="inlineStr"/>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>1-maktab</t>
+          <t>Shahrisabz pedagogika kolleji</t>
         </is>
       </c>
       <c r="S38" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T38" s="5" t="inlineStr"/>
@@ -76905,8 +76825,88 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Talabalar safidan chiqarilganlar</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr"/>
+      <c r="E39" s="11" t="inlineStr"/>
+      <c r="F39" s="11" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>AD8888020</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>62609075590027</t>
+        </is>
+      </c>
+      <c r="L39" s="11" t="inlineStr">
+        <is>
+          <t>07,10,2024</t>
+        </is>
+      </c>
+      <c r="M39" s="11" t="inlineStr"/>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O39" s="10" t="inlineStr"/>
+      <c r="P39" s="8" t="inlineStr">
+        <is>
+          <t>UM 03295463</t>
+        </is>
+      </c>
+      <c r="Q39" s="10" t="inlineStr"/>
+      <c r="R39" s="10" t="inlineStr">
+        <is>
+          <t>1-maktab</t>
+        </is>
+      </c>
+      <c r="S39" s="11" t="inlineStr">
+        <is>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T39" s="11" t="inlineStr"/>
+      <c r="U39" s="11" t="inlineStr"/>
+      <c r="V39" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W39" s="6" t="inlineStr"/>
+      <c r="X39" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X38"/>
+  <autoFilter ref="A1:X39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -41608,9 +41608,9 @@
       </c>
       <c r="V442" s="4" t="inlineStr"/>
       <c r="W442" s="6" t="inlineStr"/>
-      <c r="X442" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X442" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -61480,9 +61480,9 @@
       </c>
       <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="6" t="inlineStr"/>
-      <c r="X26" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -39516,9 +39516,9 @@
         </is>
       </c>
       <c r="W419" s="6" t="inlineStr"/>
-      <c r="X419" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X419" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
@@ -57347,9 +57347,9 @@
         </is>
       </c>
       <c r="W21" s="6" t="inlineStr"/>
-      <c r="X21" s="15" t="inlineStr">
-        <is>
-          <t>KUTILMOQDA</t>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -43512,9 +43512,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X463" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X463" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -73380,9 +73380,9 @@
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X31" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X31" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>

--- a/data/Talabalar_Yangilangan_Royxat.xlsx
+++ b/data/Talabalar_Yangilangan_Royxat.xlsx
@@ -17,8 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safdan chiqarilganlar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$566</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jami'!$A$1:$X$567</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26-01 (Mirzayeva.D)'!$A$1:$X$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'26-02 (Ochilov.D)'!$A$1:$X$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26-03 (To''rayeva.S)'!$A$1:$X$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26-04 (Hamdamova.M)'!$A$1:$X$32</definedName>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X566"/>
+  <dimension ref="A1:X567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -48227,73 +48227,97 @@
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>25-22</t>
+          <t>26-01</t>
         </is>
       </c>
       <c r="C514" s="3" t="inlineStr">
         <is>
-          <t>Xayrullayeva Asolat</t>
-        </is>
-      </c>
-      <c r="D514" s="4" t="inlineStr"/>
+          <t>Xayrullayeva Asila</t>
+        </is>
+      </c>
+      <c r="D514" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E514" s="5" t="inlineStr"/>
-      <c r="F514" s="5" t="inlineStr"/>
+      <c r="F514" s="5" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
       <c r="G514" s="5" t="inlineStr">
         <is>
-          <t>Bahriddin qizi</t>
+          <t>Azamat qizi</t>
         </is>
       </c>
       <c r="H514" s="4" t="inlineStr">
         <is>
-          <t>Xayrullayeva Asolat Bahriddin qizi</t>
+          <t>Xayrullayeva Asila Azamat qizi</t>
         </is>
       </c>
       <c r="I514" s="3" t="inlineStr"/>
       <c r="J514" s="5" t="inlineStr">
         <is>
-          <t>AC0197947</t>
+          <t>AE6045063</t>
         </is>
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
-          <t>62310026500029</t>
+          <t>62103095680022</t>
         </is>
       </c>
       <c r="L514" s="5" t="inlineStr">
         <is>
-          <t>13.11.2018</t>
+          <t>26.01.2026</t>
         </is>
       </c>
       <c r="M514" s="5" t="inlineStr">
         <is>
-          <t>23.10.2002</t>
-        </is>
-      </c>
-      <c r="N514" s="5" t="inlineStr"/>
-      <c r="O514" s="4" t="inlineStr"/>
+          <t>21.03.2009</t>
+        </is>
+      </c>
+      <c r="N514" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O514" s="4" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
       <c r="P514" s="2" t="inlineStr">
         <is>
-          <t>IM 000125</t>
+          <t>UM 03728305</t>
         </is>
       </c>
       <c r="Q514" s="4" t="inlineStr"/>
-      <c r="R514" s="4" t="inlineStr"/>
+      <c r="R514" s="4" t="inlineStr">
+        <is>
+          <t>Kitob tumani 9-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
       <c r="S514" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T514" s="5" t="inlineStr"/>
-      <c r="U514" s="5" t="inlineStr"/>
-      <c r="V514" s="4" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
-        </is>
-      </c>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T514" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U514" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V514" s="4" t="inlineStr"/>
       <c r="W514" s="6" t="inlineStr"/>
-      <c r="X514" s="7" t="inlineStr">
-        <is>
-          <t>TASDIQLANDI</t>
+      <c r="X514" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
         </is>
       </c>
     </row>
@@ -48308,7 +48332,7 @@
       </c>
       <c r="C515" s="9" t="inlineStr">
         <is>
-          <t>Xayrullayeva Ozoda</t>
+          <t>Xayrullayeva Asolat</t>
         </is>
       </c>
       <c r="D515" s="10" t="inlineStr"/>
@@ -48316,55 +48340,47 @@
       <c r="F515" s="11" t="inlineStr"/>
       <c r="G515" s="11" t="inlineStr">
         <is>
-          <t>Tashbova qizi</t>
+          <t>Bahriddin qizi</t>
         </is>
       </c>
       <c r="H515" s="10" t="inlineStr">
         <is>
-          <t>Xayrullayeva Ozoda Tashbova qizi</t>
+          <t>Xayrullayeva Asolat Bahriddin qizi</t>
         </is>
       </c>
       <c r="I515" s="9" t="inlineStr"/>
       <c r="J515" s="11" t="inlineStr">
         <is>
-          <t>AD2228454</t>
+          <t>AC0197947</t>
         </is>
       </c>
       <c r="K515" s="8" t="inlineStr">
         <is>
-          <t>62401065590055</t>
+          <t>62310026500029</t>
         </is>
       </c>
       <c r="L515" s="11" t="inlineStr">
         <is>
-          <t>22.12.2022</t>
+          <t>13.11.2018</t>
         </is>
       </c>
       <c r="M515" s="11" t="inlineStr">
         <is>
-          <t>24.01.2006</t>
-        </is>
-      </c>
-      <c r="N515" s="11" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
+          <t>23.10.2002</t>
+        </is>
+      </c>
+      <c r="N515" s="11" t="inlineStr"/>
       <c r="O515" s="10" t="inlineStr"/>
       <c r="P515" s="8" t="inlineStr">
         <is>
-          <t>PT 0097952</t>
+          <t>IM 000125</t>
         </is>
       </c>
       <c r="Q515" s="10" t="inlineStr"/>
-      <c r="R515" s="10" t="inlineStr">
-        <is>
-          <t>2-sonli kasb-hunar maktabi</t>
-        </is>
-      </c>
+      <c r="R515" s="10" t="inlineStr"/>
       <c r="S515" s="11" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T515" s="11" t="inlineStr"/>
@@ -48387,12 +48403,12 @@
       </c>
       <c r="B516" s="2" t="inlineStr">
         <is>
-          <t>24-15</t>
+          <t>25-22</t>
         </is>
       </c>
       <c r="C516" s="3" t="inlineStr">
         <is>
-          <t>Xayrullayeva Sevinch</t>
+          <t>Xayrullayeva Ozoda</t>
         </is>
       </c>
       <c r="D516" s="4" t="inlineStr"/>
@@ -48400,33 +48416,33 @@
       <c r="F516" s="5" t="inlineStr"/>
       <c r="G516" s="5" t="inlineStr">
         <is>
-          <t>Toxir qizi</t>
+          <t>Tashbova qizi</t>
         </is>
       </c>
       <c r="H516" s="4" t="inlineStr">
         <is>
-          <t>Xayrullayeva Sevinch Toxir qizi</t>
+          <t>Xayrullayeva Ozoda Tashbova qizi</t>
         </is>
       </c>
       <c r="I516" s="3" t="inlineStr"/>
       <c r="J516" s="5" t="inlineStr">
         <is>
-          <t>AD0139881</t>
+          <t>AD2228454</t>
         </is>
       </c>
       <c r="K516" s="2" t="inlineStr">
         <is>
-          <t>62010045590044</t>
+          <t>62401065590055</t>
         </is>
       </c>
       <c r="L516" s="5" t="inlineStr">
         <is>
-          <t>09.02.2021</t>
+          <t>22.12.2022</t>
         </is>
       </c>
       <c r="M516" s="5" t="inlineStr">
         <is>
-          <t>20.10.2004</t>
+          <t>24.01.2006</t>
         </is>
       </c>
       <c r="N516" s="5" t="inlineStr">
@@ -48437,18 +48453,18 @@
       <c r="O516" s="4" t="inlineStr"/>
       <c r="P516" s="2" t="inlineStr">
         <is>
-          <t>UM 1318554</t>
+          <t>PT 0097952</t>
         </is>
       </c>
       <c r="Q516" s="4" t="inlineStr"/>
       <c r="R516" s="4" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>2-sonli kasb-hunar maktabi</t>
         </is>
       </c>
       <c r="S516" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T516" s="5" t="inlineStr"/>
@@ -48471,62 +48487,46 @@
       </c>
       <c r="B517" s="8" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>24-15</t>
         </is>
       </c>
       <c r="C517" s="9" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida</t>
-        </is>
-      </c>
-      <c r="D517" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E517" s="11" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="F517" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Xayrullayeva Sevinch</t>
+        </is>
+      </c>
+      <c r="D517" s="10" t="inlineStr"/>
+      <c r="E517" s="11" t="inlineStr"/>
+      <c r="F517" s="11" t="inlineStr"/>
       <c r="G517" s="11" t="inlineStr">
         <is>
-          <t>Safar qizi</t>
+          <t>Toxir qizi</t>
         </is>
       </c>
       <c r="H517" s="10" t="inlineStr">
         <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
-        </is>
-      </c>
-      <c r="I517" s="9" t="inlineStr">
-        <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
-        </is>
-      </c>
+          <t>Xayrullayeva Sevinch Toxir qizi</t>
+        </is>
+      </c>
+      <c r="I517" s="9" t="inlineStr"/>
       <c r="J517" s="11" t="inlineStr">
         <is>
-          <t>AD9786798</t>
+          <t>AD0139881</t>
         </is>
       </c>
       <c r="K517" s="8" t="inlineStr">
         <is>
-          <t>61911085590096</t>
+          <t>62010045590044</t>
         </is>
       </c>
       <c r="L517" s="11" t="inlineStr">
         <is>
-          <t>12.12.2024</t>
+          <t>09.02.2021</t>
         </is>
       </c>
       <c r="M517" s="11" t="inlineStr">
         <is>
-          <t>19.11.2008</t>
+          <t>20.10.2004</t>
         </is>
       </c>
       <c r="N517" s="11" t="inlineStr">
@@ -48534,43 +48534,31 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O517" s="10" t="inlineStr">
-        <is>
-          <t>Xayrullayeva Umida Safar qizi</t>
-        </is>
-      </c>
+      <c r="O517" s="10" t="inlineStr"/>
       <c r="P517" s="8" t="inlineStr">
         <is>
-          <t>PT 0025701</t>
+          <t>UM 1318554</t>
         </is>
       </c>
       <c r="Q517" s="10" t="inlineStr"/>
       <c r="R517" s="10" t="inlineStr">
         <is>
-          <t>Kitob tuman 1-son texnikumi</t>
+          <t>7-maktab</t>
         </is>
       </c>
       <c r="S517" s="11" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T517" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U517" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V517" s="10" t="inlineStr"/>
-      <c r="W517" s="6" t="inlineStr">
-        <is>
-          <t>TEKSHIRILMAGAN</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T517" s="11" t="inlineStr"/>
+      <c r="U517" s="11" t="inlineStr"/>
+      <c r="V517" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W517" s="6" t="inlineStr"/>
       <c r="X517" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -48583,46 +48571,62 @@
       </c>
       <c r="B518" s="2" t="inlineStr">
         <is>
-          <t>24-13</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C518" s="3" t="inlineStr">
         <is>
-          <t>Xazratova Gulhayo</t>
-        </is>
-      </c>
-      <c r="D518" s="4" t="inlineStr"/>
-      <c r="E518" s="5" t="inlineStr"/>
-      <c r="F518" s="5" t="inlineStr"/>
+          <t>Xayrullayeva Umida</t>
+        </is>
+      </c>
+      <c r="D518" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E518" s="5" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F518" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G518" s="5" t="inlineStr">
         <is>
-          <t>Sirojiddin qizi</t>
+          <t>Safar qizi</t>
         </is>
       </c>
       <c r="H518" s="4" t="inlineStr">
         <is>
-          <t>Xazratova Gulhayo Sirojiddin qizi</t>
-        </is>
-      </c>
-      <c r="I518" s="3" t="inlineStr"/>
+          <t>Xayrullayeva Umida Safar qizi</t>
+        </is>
+      </c>
+      <c r="I518" s="3" t="inlineStr">
+        <is>
+          <t>Xayrullayeva Umida Safar qizi</t>
+        </is>
+      </c>
       <c r="J518" s="5" t="inlineStr">
         <is>
-          <t>AD2073294</t>
+          <t>AD9786798</t>
         </is>
       </c>
       <c r="K518" s="2" t="inlineStr">
         <is>
-          <t>60511065590033</t>
+          <t>61911085590096</t>
         </is>
       </c>
       <c r="L518" s="5" t="inlineStr">
         <is>
-          <t>24.11.2022</t>
+          <t>12.12.2024</t>
         </is>
       </c>
       <c r="M518" s="5" t="inlineStr">
         <is>
-          <t>05.11.2006</t>
+          <t>19.11.2008</t>
         </is>
       </c>
       <c r="N518" s="5" t="inlineStr">
@@ -48630,31 +48634,43 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O518" s="4" t="inlineStr"/>
+      <c r="O518" s="4" t="inlineStr">
+        <is>
+          <t>Xayrullayeva Umida Safar qizi</t>
+        </is>
+      </c>
       <c r="P518" s="2" t="inlineStr">
         <is>
-          <t>UM 02171904</t>
+          <t>PT 0025701</t>
         </is>
       </c>
       <c r="Q518" s="4" t="inlineStr"/>
       <c r="R518" s="4" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>Kitob tuman 1-son texnikumi</t>
         </is>
       </c>
       <c r="S518" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T518" s="5" t="inlineStr"/>
-      <c r="U518" s="5" t="inlineStr"/>
-      <c r="V518" s="4" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: 3-kurs</t>
-        </is>
-      </c>
-      <c r="W518" s="6" t="inlineStr"/>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T518" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U518" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V518" s="4" t="inlineStr"/>
+      <c r="W518" s="6" t="inlineStr">
+        <is>
+          <t>TEKSHIRILMAGAN</t>
+        </is>
+      </c>
       <c r="X518" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -48667,108 +48683,78 @@
       </c>
       <c r="B519" s="8" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>24-13</t>
         </is>
       </c>
       <c r="C519" s="9" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor</t>
-        </is>
-      </c>
-      <c r="D519" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E519" s="11" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="F519" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-14 00:00:00</t>
-        </is>
-      </c>
+          <t>Xazratova Gulhayo</t>
+        </is>
+      </c>
+      <c r="D519" s="10" t="inlineStr"/>
+      <c r="E519" s="11" t="inlineStr"/>
+      <c r="F519" s="11" t="inlineStr"/>
       <c r="G519" s="11" t="inlineStr">
         <is>
-          <t>Azim qizi</t>
+          <t>Sirojiddin qizi</t>
         </is>
       </c>
       <c r="H519" s="10" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
-        </is>
-      </c>
-      <c r="I519" s="9" t="inlineStr">
-        <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
-        </is>
-      </c>
+          <t>Xazratova Gulhayo Sirojiddin qizi</t>
+        </is>
+      </c>
+      <c r="I519" s="9" t="inlineStr"/>
       <c r="J519" s="11" t="inlineStr">
         <is>
-          <t>AD4186543</t>
+          <t>AD2073294</t>
         </is>
       </c>
       <c r="K519" s="8" t="inlineStr">
         <is>
-          <t>62104025680040</t>
+          <t>60511065590033</t>
         </is>
       </c>
       <c r="L519" s="11" t="inlineStr">
         <is>
-          <t>07.08.2023</t>
+          <t>24.11.2022</t>
         </is>
       </c>
       <c r="M519" s="11" t="inlineStr">
         <is>
-          <t>21.04.2002</t>
+          <t>05.11.2006</t>
         </is>
       </c>
       <c r="N519" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O519" s="10" t="inlineStr">
-        <is>
-          <t>Xo'jaqulova Navbahor Azim qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O519" s="10" t="inlineStr"/>
       <c r="P519" s="8" t="inlineStr">
         <is>
-          <t>UM 0086260</t>
+          <t>UM 02171904</t>
         </is>
       </c>
       <c r="Q519" s="10" t="inlineStr"/>
       <c r="R519" s="10" t="inlineStr">
         <is>
-          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>7-maktab</t>
         </is>
       </c>
       <c r="S519" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T519" s="11" t="n">
-        <v>2019</v>
-      </c>
-      <c r="U519" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T519" s="11" t="inlineStr"/>
+      <c r="U519" s="11" t="inlineStr"/>
       <c r="V519" s="10" t="inlineStr">
         <is>
-          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W519" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>2025-2026 kontingenti: 3-kurs</t>
+        </is>
+      </c>
+      <c r="W519" s="6" t="inlineStr"/>
       <c r="X519" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -48781,46 +48767,62 @@
       </c>
       <c r="B520" s="2" t="inlineStr">
         <is>
-          <t>25-19</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C520" s="3" t="inlineStr">
         <is>
-          <t>Xolboboyeva Jasmina</t>
-        </is>
-      </c>
-      <c r="D520" s="4" t="inlineStr"/>
-      <c r="E520" s="5" t="inlineStr"/>
-      <c r="F520" s="5" t="inlineStr"/>
+          <t>Xo'jaqulova Navbahor</t>
+        </is>
+      </c>
+      <c r="D520" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E520" s="5" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="F520" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
       <c r="G520" s="5" t="inlineStr">
         <is>
-          <t>Nurullo qizi</t>
+          <t>Azim qizi</t>
         </is>
       </c>
       <c r="H520" s="4" t="inlineStr">
         <is>
-          <t>Xolboboyeva Jasmina Nurullo qizi</t>
-        </is>
-      </c>
-      <c r="I520" s="3" t="inlineStr"/>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
+        </is>
+      </c>
+      <c r="I520" s="3" t="inlineStr">
+        <is>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
+        </is>
+      </c>
       <c r="J520" s="5" t="inlineStr">
         <is>
-          <t>AD4730304</t>
+          <t>AD4186543</t>
         </is>
       </c>
       <c r="K520" s="2" t="inlineStr">
         <is>
-          <t>62607065680059</t>
+          <t>62104025680040</t>
         </is>
       </c>
       <c r="L520" s="5" t="inlineStr">
         <is>
-          <t>28.09.2023</t>
+          <t>07.08.2023</t>
         </is>
       </c>
       <c r="M520" s="5" t="inlineStr">
         <is>
-          <t>26.07.2006</t>
+          <t>21.04.2002</t>
         </is>
       </c>
       <c r="N520" s="5" t="inlineStr">
@@ -48828,31 +48830,45 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O520" s="4" t="inlineStr"/>
+      <c r="O520" s="4" t="inlineStr">
+        <is>
+          <t>Xo'jaqulova Navbahor Azim qizi</t>
+        </is>
+      </c>
       <c r="P520" s="2" t="inlineStr">
         <is>
-          <t>UM 02149968</t>
+          <t>UM 0086260</t>
         </is>
       </c>
       <c r="Q520" s="4" t="inlineStr"/>
       <c r="R520" s="4" t="inlineStr">
         <is>
-          <t>5-maktab</t>
+          <t>63-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S520" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T520" s="5" t="inlineStr"/>
-      <c r="U520" s="5" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T520" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="U520" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V520" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
-        </is>
-      </c>
-      <c r="W520" s="6" t="inlineStr"/>
+          <t>Xo'jaqulova Navbaxor Azim qizi 302.docx faylidan to'liq kiritildi</t>
+        </is>
+      </c>
+      <c r="W520" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X520" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -48865,12 +48881,12 @@
       </c>
       <c r="B521" s="8" t="inlineStr">
         <is>
-          <t>25-17</t>
+          <t>25-19</t>
         </is>
       </c>
       <c r="C521" s="9" t="inlineStr">
         <is>
-          <t>Xolbutayeva Xusniya</t>
+          <t>Xolboboyeva Jasmina</t>
         </is>
       </c>
       <c r="D521" s="10" t="inlineStr"/>
@@ -48878,55 +48894,55 @@
       <c r="F521" s="11" t="inlineStr"/>
       <c r="G521" s="11" t="inlineStr">
         <is>
-          <t>Mahmasodiq qizi</t>
+          <t>Nurullo qizi</t>
         </is>
       </c>
       <c r="H521" s="10" t="inlineStr">
         <is>
-          <t>Xolbutayeva Xusniya Mahmasodiq qizi</t>
+          <t>Xolboboyeva Jasmina Nurullo qizi</t>
         </is>
       </c>
       <c r="I521" s="9" t="inlineStr"/>
       <c r="J521" s="11" t="inlineStr">
         <is>
-          <t>AC0368170</t>
+          <t>AD4730304</t>
         </is>
       </c>
       <c r="K521" s="8" t="inlineStr">
         <is>
-          <t>60205005730033</t>
+          <t>62607065680059</t>
         </is>
       </c>
       <c r="L521" s="11" t="inlineStr">
         <is>
-          <t>04.12.2018</t>
+          <t>28.09.2023</t>
         </is>
       </c>
       <c r="M521" s="11" t="inlineStr">
         <is>
-          <t>02.05.2000</t>
+          <t>26.07.2006</t>
         </is>
       </c>
       <c r="N521" s="11" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O521" s="10" t="inlineStr"/>
       <c r="P521" s="8" t="inlineStr">
         <is>
-          <t>K 5495190</t>
+          <t>UM 02149968</t>
         </is>
       </c>
       <c r="Q521" s="10" t="inlineStr"/>
       <c r="R521" s="10" t="inlineStr">
         <is>
-          <t>Yakkabog' axborot texnalogiyalari kolleji</t>
+          <t>5-maktab</t>
         </is>
       </c>
       <c r="S521" s="11" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T521" s="11" t="inlineStr"/>
@@ -48949,12 +48965,12 @@
       </c>
       <c r="B522" s="2" t="inlineStr">
         <is>
-          <t>24-15</t>
+          <t>25-17</t>
         </is>
       </c>
       <c r="C522" s="3" t="inlineStr">
         <is>
-          <t>Xoliqova Marjona</t>
+          <t>Xolbutayeva Xusniya</t>
         </is>
       </c>
       <c r="D522" s="4" t="inlineStr"/>
@@ -48962,50 +48978,50 @@
       <c r="F522" s="5" t="inlineStr"/>
       <c r="G522" s="5" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Mahmasodiq qizi</t>
         </is>
       </c>
       <c r="H522" s="4" t="inlineStr">
         <is>
-          <t>Xoliqova Marjona Baxtiyor qizi</t>
+          <t>Xolbutayeva Xusniya Mahmasodiq qizi</t>
         </is>
       </c>
       <c r="I522" s="3" t="inlineStr"/>
       <c r="J522" s="5" t="inlineStr">
         <is>
-          <t>AB9215776</t>
+          <t>AC0368170</t>
         </is>
       </c>
       <c r="K522" s="2" t="inlineStr">
         <is>
-          <t>60608015720029</t>
+          <t>60205005730033</t>
         </is>
       </c>
       <c r="L522" s="5" t="inlineStr">
         <is>
-          <t>03.04.2018</t>
+          <t>04.12.2018</t>
         </is>
       </c>
       <c r="M522" s="5" t="inlineStr">
         <is>
-          <t>06.08.2001</t>
+          <t>02.05.2000</t>
         </is>
       </c>
       <c r="N522" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O522" s="4" t="inlineStr"/>
       <c r="P522" s="2" t="inlineStr">
         <is>
-          <t>K 0349715</t>
+          <t>K 5495190</t>
         </is>
       </c>
       <c r="Q522" s="4" t="inlineStr"/>
       <c r="R522" s="4" t="inlineStr">
         <is>
-          <t>Chiroqchi qishloq-xo'jalik va xizmat ko'rsatish kolleji</t>
+          <t>Yakkabog' axborot texnalogiyalari kolleji</t>
         </is>
       </c>
       <c r="S522" s="5" t="inlineStr">
@@ -49033,72 +49049,68 @@
       </c>
       <c r="B523" s="8" t="inlineStr">
         <is>
-          <t>25-20</t>
+          <t>24-15</t>
         </is>
       </c>
       <c r="C523" s="9" t="inlineStr">
         <is>
-          <t>Xoliqulova Nozima</t>
+          <t>Xoliqova Marjona</t>
         </is>
       </c>
       <c r="D523" s="10" t="inlineStr"/>
-      <c r="E523" s="11" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
+      <c r="E523" s="11" t="inlineStr"/>
       <c r="F523" s="11" t="inlineStr"/>
       <c r="G523" s="11" t="inlineStr">
         <is>
-          <t>Qalandar qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H523" s="10" t="inlineStr">
         <is>
-          <t>Xoliqulova Nozima Qalandar qizi</t>
+          <t>Xoliqova Marjona Baxtiyor qizi</t>
         </is>
       </c>
       <c r="I523" s="9" t="inlineStr"/>
       <c r="J523" s="11" t="inlineStr">
         <is>
-          <t>AD9626141</t>
+          <t>AB9215776</t>
         </is>
       </c>
       <c r="K523" s="8" t="inlineStr">
         <is>
-          <t>62503085590032</t>
+          <t>60608015720029</t>
         </is>
       </c>
       <c r="L523" s="11" t="inlineStr">
         <is>
-          <t>30.11.2024</t>
+          <t>03.04.2018</t>
         </is>
       </c>
       <c r="M523" s="11" t="inlineStr">
         <is>
-          <t>25.03.2008</t>
+          <t>06.08.2001</t>
         </is>
       </c>
       <c r="N523" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O523" s="10" t="inlineStr"/>
       <c r="P523" s="8" t="inlineStr">
         <is>
-          <t>UM 03298056</t>
+          <t>K 0349715</t>
         </is>
       </c>
       <c r="Q523" s="10" t="inlineStr"/>
       <c r="R523" s="10" t="inlineStr">
         <is>
-          <t>43-maktab</t>
+          <t>Chiroqchi qishloq-xo'jalik va xizmat ko'rsatish kolleji</t>
         </is>
       </c>
       <c r="S523" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Kollej</t>
         </is>
       </c>
       <c r="T523" s="11" t="inlineStr"/>
@@ -49121,63 +49133,67 @@
       </c>
       <c r="B524" s="2" t="inlineStr">
         <is>
-          <t>25-22</t>
+          <t>25-20</t>
         </is>
       </c>
       <c r="C524" s="3" t="inlineStr">
         <is>
-          <t>Xolmamatova Nodira</t>
+          <t>Xoliqulova Nozima</t>
         </is>
       </c>
       <c r="D524" s="4" t="inlineStr"/>
-      <c r="E524" s="5" t="inlineStr"/>
+      <c r="E524" s="5" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
       <c r="F524" s="5" t="inlineStr"/>
       <c r="G524" s="5" t="inlineStr">
         <is>
-          <t>Bekmurod qizi</t>
+          <t>Qalandar qizi</t>
         </is>
       </c>
       <c r="H524" s="4" t="inlineStr">
         <is>
-          <t>Xolmamatova Nodira Bekmurod qizi</t>
+          <t>Xoliqulova Nozima Qalandar qizi</t>
         </is>
       </c>
       <c r="I524" s="3" t="inlineStr"/>
       <c r="J524" s="5" t="inlineStr">
         <is>
-          <t>AC2113849</t>
+          <t>AD9626141</t>
         </is>
       </c>
       <c r="K524" s="2" t="inlineStr">
         <is>
-          <t>60704025680095</t>
+          <t>62503085590032</t>
         </is>
       </c>
       <c r="L524" s="5" t="inlineStr">
         <is>
-          <t>30.07.2019</t>
+          <t>30.11.2024</t>
         </is>
       </c>
       <c r="M524" s="5" t="inlineStr">
         <is>
-          <t>07.04.2002</t>
+          <t>25.03.2008</t>
         </is>
       </c>
       <c r="N524" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O524" s="4" t="inlineStr"/>
       <c r="P524" s="2" t="inlineStr">
         <is>
-          <t>UM 0418516</t>
+          <t>UM 03298056</t>
         </is>
       </c>
       <c r="Q524" s="4" t="inlineStr"/>
       <c r="R524" s="4" t="inlineStr">
         <is>
-          <t>17-maktab</t>
+          <t>43-maktab</t>
         </is>
       </c>
       <c r="S524" s="5" t="inlineStr">
@@ -49205,110 +49221,78 @@
       </c>
       <c r="B525" s="8" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>25-22</t>
         </is>
       </c>
       <c r="C525" s="9" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista</t>
+          <t>Xolmamatova Nodira</t>
         </is>
       </c>
       <c r="D525" s="10" t="inlineStr"/>
-      <c r="E525" s="11" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="F525" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E525" s="11" t="inlineStr"/>
+      <c r="F525" s="11" t="inlineStr"/>
       <c r="G525" s="11" t="inlineStr">
         <is>
-          <t>Sobir qizi</t>
+          <t>Bekmurod qizi</t>
         </is>
       </c>
       <c r="H525" s="10" t="inlineStr">
         <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
-        </is>
-      </c>
-      <c r="I525" s="9" t="inlineStr">
-        <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
-        </is>
-      </c>
+          <t>Xolmamatova Nodira Bekmurod qizi</t>
+        </is>
+      </c>
+      <c r="I525" s="9" t="inlineStr"/>
       <c r="J525" s="11" t="inlineStr">
         <is>
-          <t>AE4328716</t>
+          <t>AC2113849</t>
         </is>
       </c>
       <c r="K525" s="8" t="inlineStr">
         <is>
-          <t>60201085720092</t>
+          <t>60704025680095</t>
         </is>
       </c>
       <c r="L525" s="11" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>30.07.2019</t>
         </is>
       </c>
       <c r="M525" s="11" t="inlineStr">
         <is>
-          <t>02.01.2008</t>
+          <t>07.04.2002</t>
         </is>
       </c>
       <c r="N525" s="11" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O525" s="10" t="inlineStr">
-        <is>
-          <t>Xolmamatova Shoxista Sobir qizi</t>
-        </is>
-      </c>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O525" s="10" t="inlineStr"/>
       <c r="P525" s="8" t="inlineStr">
         <is>
-          <t>UM 03718337</t>
-        </is>
-      </c>
-      <c r="Q525" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0418516</t>
+        </is>
+      </c>
+      <c r="Q525" s="10" t="inlineStr"/>
       <c r="R525" s="10" t="inlineStr">
         <is>
-          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>17-maktab</t>
         </is>
       </c>
       <c r="S525" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T525" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U525" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T525" s="11" t="inlineStr"/>
+      <c r="U525" s="11" t="inlineStr"/>
       <c r="V525" s="10" t="inlineStr">
         <is>
-          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
-        </is>
-      </c>
-      <c r="W525" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W525" s="6" t="inlineStr"/>
       <c r="X525" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -49326,17 +49310,13 @@
       </c>
       <c r="C526" s="3" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch</t>
-        </is>
-      </c>
-      <c r="D526" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xolmamatova Shoxista</t>
+        </is>
+      </c>
+      <c r="D526" s="4" t="inlineStr"/>
       <c r="E526" s="5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F526" s="5" t="inlineStr">
@@ -49346,62 +49326,62 @@
       </c>
       <c r="G526" s="5" t="inlineStr">
         <is>
-          <t>Isomiddin qizi</t>
+          <t>Sobir qizi</t>
         </is>
       </c>
       <c r="H526" s="4" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="I526" s="3" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="J526" s="5" t="inlineStr">
         <is>
-          <t>AE4729924</t>
+          <t>AE4328716</t>
         </is>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
-          <t>62511085730064</t>
+          <t>60201085720092</t>
         </is>
       </c>
       <c r="L526" s="5" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="M526" s="5" t="inlineStr">
         <is>
-          <t>25.11.2008</t>
+          <t>02.01.2008</t>
         </is>
       </c>
       <c r="N526" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
+          <t>Chiroqchi tumani</t>
         </is>
       </c>
       <c r="O526" s="4" t="inlineStr">
         <is>
-          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
+          <t>Xolmamatova Shoxista Sobir qizi</t>
         </is>
       </c>
       <c r="P526" s="2" t="inlineStr">
         <is>
-          <t>UM 03758009</t>
+          <t>UM 03718337</t>
         </is>
       </c>
       <c r="Q526" s="4" t="inlineStr">
         <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4160257/3908748/b21b95c1-e731-4c4b-978a-b67116d7e66e?preview=true</t>
         </is>
       </c>
       <c r="R526" s="4" t="inlineStr">
         <is>
-          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>36-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S526" s="5" t="inlineStr">
@@ -49419,7 +49399,11 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V526" s="4" t="inlineStr"/>
+      <c r="V526" s="4" t="inlineStr">
+        <is>
+          <t>Familiyasi Xolmamatova Shoxista Sobir qizi deb to'g'rilandi (#243)</t>
+        </is>
+      </c>
       <c r="W526" s="13" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -49437,12 +49421,12 @@
       </c>
       <c r="B527" s="8" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C527" s="9" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso</t>
+          <t>Xolmaxmatova Sevinch</t>
         </is>
       </c>
       <c r="D527" s="10" t="inlineStr">
@@ -49452,7 +49436,7 @@
       </c>
       <c r="E527" s="11" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F527" s="11" t="inlineStr">
@@ -49462,37 +49446,37 @@
       </c>
       <c r="G527" s="11" t="inlineStr">
         <is>
-          <t>Xushvaq qizi</t>
+          <t>Isomiddin qizi</t>
         </is>
       </c>
       <c r="H527" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="I527" s="9" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="J527" s="11" t="inlineStr">
         <is>
-          <t>AD8362477</t>
+          <t>AE4729924</t>
         </is>
       </c>
       <c r="K527" s="8" t="inlineStr">
         <is>
-          <t>42601955730024</t>
+          <t>62511085730064</t>
         </is>
       </c>
       <c r="L527" s="11" t="inlineStr">
         <is>
-          <t>23.08.2024</t>
+          <t>22.10.2025</t>
         </is>
       </c>
       <c r="M527" s="11" t="inlineStr">
         <is>
-          <t>26.01.1995</t>
+          <t>25.11.2008</t>
         </is>
       </c>
       <c r="N527" s="11" t="inlineStr">
@@ -49502,28 +49486,32 @@
       </c>
       <c r="O527" s="10" t="inlineStr">
         <is>
-          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
+          <t>Xolmaxmatova Sevinch Isomiddin qizi</t>
         </is>
       </c>
       <c r="P527" s="8" t="inlineStr">
         <is>
-          <t>K 3418837</t>
-        </is>
-      </c>
-      <c r="Q527" s="10" t="inlineStr"/>
+          <t>UM 03758009</t>
+        </is>
+      </c>
+      <c r="Q527" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3845465/3883622/6f79b318-a4e1-46cb-ab79-97546eb5163a?preview=true</t>
+        </is>
+      </c>
       <c r="R527" s="10" t="inlineStr">
         <is>
-          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
+          <t>69-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S527" s="11" t="inlineStr">
         <is>
-          <t>Diplom</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T527" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U527" s="7" t="inlineStr">
@@ -49531,14 +49519,10 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V527" s="10" t="inlineStr">
-        <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
-        </is>
-      </c>
-      <c r="W527" s="14" t="inlineStr">
-        <is>
-          <t>Pasport: FARQ</t>
+      <c r="V527" s="10" t="inlineStr"/>
+      <c r="W527" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X527" s="7" t="inlineStr">
@@ -49553,12 +49537,12 @@
       </c>
       <c r="B528" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C528" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura</t>
+          <t>Xolmirzayeva Zebuniso</t>
         </is>
       </c>
       <c r="D528" s="4" t="inlineStr">
@@ -49568,81 +49552,79 @@
       </c>
       <c r="E528" s="5" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F528" s="5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:00:00</t>
+          <t>2026-09-02 00:00:00</t>
         </is>
       </c>
       <c r="G528" s="5" t="inlineStr">
         <is>
-          <t>Dilmurod qizi</t>
+          <t>Xushvaq qizi</t>
         </is>
       </c>
       <c r="H528" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="I528" s="3" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
       <c r="J528" s="5" t="inlineStr">
         <is>
-          <t>AE1516812</t>
+          <t>AD8362477</t>
         </is>
       </c>
       <c r="K528" s="2" t="inlineStr">
         <is>
-          <t>60110085590193</t>
+          <t>42601955730024</t>
         </is>
       </c>
       <c r="L528" s="5" t="inlineStr">
         <is>
-          <t>06.02.2025</t>
+          <t>23.08.2024</t>
         </is>
       </c>
       <c r="M528" s="5" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
+          <t>26.01.1995</t>
         </is>
       </c>
       <c r="N528" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O528" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi</t>
+          <t>Xolmirzayeva Zebiniso Xushvaqt qizi</t>
         </is>
       </c>
       <c r="P528" s="2" t="inlineStr">
         <is>
-          <t>UM 03755333</t>
-        </is>
-      </c>
-      <c r="Q528" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
-        </is>
-      </c>
+          <t>K 3418837</t>
+        </is>
+      </c>
+      <c r="Q528" s="4" t="inlineStr"/>
       <c r="R528" s="4" t="inlineStr">
         <is>
-          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Jakkabog maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
       <c r="S528" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T528" s="5" t="n">
-        <v>2026</v>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T528" s="5" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
       </c>
       <c r="U528" s="7" t="inlineStr">
         <is>
@@ -49651,12 +49633,12 @@
       </c>
       <c r="V528" s="4" t="inlineStr">
         <is>
-          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
-        </is>
-      </c>
-      <c r="W528" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'XOLMIRZAYEVA ZEBUNISO' | bazada: 'Xolmirzayeva Zebiniso'</t>
+        </is>
+      </c>
+      <c r="W528" s="14" t="inlineStr">
+        <is>
+          <t>Pasport: FARQ</t>
         </is>
       </c>
       <c r="X528" s="7" t="inlineStr">
@@ -49671,12 +49653,12 @@
       </c>
       <c r="B529" s="8" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C529" s="9" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina</t>
+          <t>Xolmurodova Dilnura</t>
         </is>
       </c>
       <c r="D529" s="10" t="inlineStr">
@@ -49686,47 +49668,47 @@
       </c>
       <c r="E529" s="11" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>307</t>
         </is>
       </c>
       <c r="F529" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:00:00</t>
+          <t>2026-09-15 00:00:00</t>
         </is>
       </c>
       <c r="G529" s="11" t="inlineStr">
         <is>
-          <t>A'zam qizi</t>
+          <t>Dilmurod qizi</t>
         </is>
       </c>
       <c r="H529" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="I529" s="9" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="J529" s="11" t="inlineStr">
         <is>
-          <t>AD2922676</t>
+          <t>AE1516812</t>
         </is>
       </c>
       <c r="K529" s="8" t="inlineStr">
         <is>
-          <t>61604065590015</t>
+          <t>60110085590193</t>
         </is>
       </c>
       <c r="L529" s="11" t="inlineStr">
         <is>
-          <t>01.04.2023</t>
+          <t>06.02.2025</t>
         </is>
       </c>
       <c r="M529" s="11" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N529" s="11" t="inlineStr">
@@ -49736,18 +49718,22 @@
       </c>
       <c r="O529" s="10" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Xolmurodova Dilnura Dilmurod qizi</t>
         </is>
       </c>
       <c r="P529" s="8" t="inlineStr">
         <is>
-          <t>UM 02172469</t>
-        </is>
-      </c>
-      <c r="Q529" s="10" t="inlineStr"/>
+          <t>UM 03755333</t>
+        </is>
+      </c>
+      <c r="Q529" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3646753/3265997/7168a42b-3c1c-4933-ac3c-05c228850986?preview=true</t>
+        </is>
+      </c>
       <c r="R529" s="10" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>60-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S529" s="11" t="inlineStr">
@@ -49755,20 +49741,22 @@
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T529" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="T529" s="11" t="n">
+        <v>2026</v>
       </c>
       <c r="U529" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V529" s="10" t="inlineStr"/>
+      <c r="V529" s="10" t="inlineStr">
+        <is>
+          <t>Xolmurodova Dilnura Dilmurod qizi 307.docx faylidan to'liq kiritildi</t>
+        </is>
+      </c>
       <c r="W529" s="13" t="inlineStr">
         <is>
-          <t>Pasport: MOS</t>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
       <c r="X529" s="7" t="inlineStr">
@@ -49783,46 +49771,62 @@
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>25-17</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C530" s="3" t="inlineStr">
         <is>
-          <t>Xomidova E'zoza</t>
-        </is>
-      </c>
-      <c r="D530" s="4" t="inlineStr"/>
-      <c r="E530" s="5" t="inlineStr"/>
-      <c r="F530" s="5" t="inlineStr"/>
+          <t>Xolmurodova Sabina</t>
+        </is>
+      </c>
+      <c r="D530" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E530" s="5" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F530" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G530" s="5" t="inlineStr">
         <is>
-          <t>Obidjon qizi</t>
+          <t>A'zam qizi</t>
         </is>
       </c>
       <c r="H530" s="4" t="inlineStr">
         <is>
-          <t>Xomidova E'zoza Obidjon qizi</t>
-        </is>
-      </c>
-      <c r="I530" s="3" t="inlineStr"/>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
+      <c r="I530" s="3" t="inlineStr">
+        <is>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
       <c r="J530" s="5" t="inlineStr">
         <is>
-          <t>AD9701049</t>
+          <t>AD2922676</t>
         </is>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
-          <t>62611075590044</t>
+          <t>61604065590015</t>
         </is>
       </c>
       <c r="L530" s="5" t="inlineStr">
         <is>
-          <t>05.12.2024</t>
+          <t>01.04.2023</t>
         </is>
       </c>
       <c r="M530" s="5" t="inlineStr">
         <is>
-          <t>26.11.2007</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="N530" s="5" t="inlineStr">
@@ -49830,31 +49834,43 @@
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O530" s="4" t="inlineStr"/>
+      <c r="O530" s="4" t="inlineStr">
+        <is>
+          <t>Xolmurodova Sabina A'zam qizi</t>
+        </is>
+      </c>
       <c r="P530" s="2" t="inlineStr">
         <is>
-          <t>UM 03296356</t>
+          <t>UM 02172469</t>
         </is>
       </c>
       <c r="Q530" s="4" t="inlineStr"/>
       <c r="R530" s="4" t="inlineStr">
         <is>
-          <t>17-maktab</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S530" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T530" s="5" t="inlineStr"/>
-      <c r="U530" s="5" t="inlineStr"/>
-      <c r="V530" s="4" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
-        </is>
-      </c>
-      <c r="W530" s="6" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T530" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U530" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V530" s="4" t="inlineStr"/>
+      <c r="W530" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
       <c r="X530" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -49867,12 +49883,12 @@
       </c>
       <c r="B531" s="8" t="inlineStr">
         <is>
-          <t>25-18</t>
+          <t>25-17</t>
         </is>
       </c>
       <c r="C531" s="9" t="inlineStr">
         <is>
-          <t>Xudoyberdiyeva Fotima</t>
+          <t>Xomidova E'zoza</t>
         </is>
       </c>
       <c r="D531" s="10" t="inlineStr"/>
@@ -49880,50 +49896,50 @@
       <c r="F531" s="11" t="inlineStr"/>
       <c r="G531" s="11" t="inlineStr">
         <is>
-          <t>Nasim qizi</t>
+          <t>Obidjon qizi</t>
         </is>
       </c>
       <c r="H531" s="10" t="inlineStr">
         <is>
-          <t>Xudoyberdiyeva Fotima Nasim qizi</t>
+          <t>Xomidova E'zoza Obidjon qizi</t>
         </is>
       </c>
       <c r="I531" s="9" t="inlineStr"/>
       <c r="J531" s="11" t="inlineStr">
         <is>
-          <t>AD6837888</t>
+          <t>AD9701049</t>
         </is>
       </c>
       <c r="K531" s="8" t="inlineStr">
         <is>
-          <t>61204085680019</t>
+          <t>62611075590044</t>
         </is>
       </c>
       <c r="L531" s="11" t="inlineStr">
         <is>
-          <t>16.04.2024</t>
+          <t>05.12.2024</t>
         </is>
       </c>
       <c r="M531" s="11" t="inlineStr">
         <is>
-          <t>12.04.2008</t>
+          <t>26.11.2007</t>
         </is>
       </c>
       <c r="N531" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
+          <t>Shahrisabz tumani</t>
         </is>
       </c>
       <c r="O531" s="10" t="inlineStr"/>
       <c r="P531" s="8" t="inlineStr">
         <is>
-          <t>UM 02151796</t>
+          <t>UM 03296356</t>
         </is>
       </c>
       <c r="Q531" s="10" t="inlineStr"/>
       <c r="R531" s="10" t="inlineStr">
         <is>
-          <t>62-maktab</t>
+          <t>17-maktab</t>
         </is>
       </c>
       <c r="S531" s="11" t="inlineStr">
@@ -49951,63 +49967,63 @@
       </c>
       <c r="B532" s="2" t="inlineStr">
         <is>
-          <t>25-21</t>
+          <t>25-18</t>
         </is>
       </c>
       <c r="C532" s="3" t="inlineStr">
         <is>
-          <t>Xudoykulova Munisa</t>
+          <t>Xudoyberdiyeva Fotima</t>
         </is>
       </c>
       <c r="D532" s="4" t="inlineStr"/>
-      <c r="E532" s="5" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
+      <c r="E532" s="5" t="inlineStr"/>
       <c r="F532" s="5" t="inlineStr"/>
       <c r="G532" s="5" t="inlineStr">
         <is>
-          <t>Muzurovna</t>
+          <t>Nasim qizi</t>
         </is>
       </c>
       <c r="H532" s="4" t="inlineStr">
         <is>
-          <t>Xudoykulova Munisa Muzurovna</t>
+          <t>Xudoyberdiyeva Fotima Nasim qizi</t>
         </is>
       </c>
       <c r="I532" s="3" t="inlineStr"/>
       <c r="J532" s="5" t="inlineStr">
         <is>
-          <t>AB3909486</t>
+          <t>AD6837888</t>
         </is>
       </c>
       <c r="K532" s="2" t="inlineStr">
         <is>
-          <t>41604892640093</t>
+          <t>61204085680019</t>
         </is>
       </c>
       <c r="L532" s="5" t="inlineStr">
         <is>
-          <t>16.05.2016</t>
+          <t>16.04.2024</t>
         </is>
       </c>
       <c r="M532" s="5" t="inlineStr">
         <is>
-          <t>16.04.1989</t>
-        </is>
-      </c>
-      <c r="N532" s="5" t="inlineStr"/>
+          <t>12.04.2008</t>
+        </is>
+      </c>
+      <c r="N532" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O532" s="4" t="inlineStr"/>
       <c r="P532" s="2" t="inlineStr">
         <is>
-          <t>O'R-SH 0661942</t>
+          <t>UM 02151796</t>
         </is>
       </c>
       <c r="Q532" s="4" t="inlineStr"/>
       <c r="R532" s="4" t="inlineStr">
         <is>
-          <t>54-maktab</t>
+          <t>62-maktab</t>
         </is>
       </c>
       <c r="S532" s="5" t="inlineStr">
@@ -50040,11 +50056,15 @@
       </c>
       <c r="C533" s="9" t="inlineStr">
         <is>
-          <t>Xudoykulova Sadorat</t>
+          <t>Xudoykulova Munisa</t>
         </is>
       </c>
       <c r="D533" s="10" t="inlineStr"/>
-      <c r="E533" s="11" t="inlineStr"/>
+      <c r="E533" s="11" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
       <c r="F533" s="11" t="inlineStr"/>
       <c r="G533" s="11" t="inlineStr">
         <is>
@@ -50053,45 +50073,41 @@
       </c>
       <c r="H533" s="10" t="inlineStr">
         <is>
-          <t>Xudoykulova Sadorat Muzurovna</t>
+          <t>Xudoykulova Munisa Muzurovna</t>
         </is>
       </c>
       <c r="I533" s="9" t="inlineStr"/>
       <c r="J533" s="11" t="inlineStr">
         <is>
-          <t>AB7071720</t>
+          <t>AB3909486</t>
         </is>
       </c>
       <c r="K533" s="8" t="inlineStr">
         <is>
-          <t>41712915680028</t>
+          <t>41604892640093</t>
         </is>
       </c>
       <c r="L533" s="11" t="inlineStr">
         <is>
-          <t>28.06.2017</t>
+          <t>16.05.2016</t>
         </is>
       </c>
       <c r="M533" s="11" t="inlineStr">
         <is>
-          <t>17.12.1991</t>
-        </is>
-      </c>
-      <c r="N533" s="11" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
+          <t>16.04.1989</t>
+        </is>
+      </c>
+      <c r="N533" s="11" t="inlineStr"/>
       <c r="O533" s="10" t="inlineStr"/>
       <c r="P533" s="8" t="inlineStr">
         <is>
-          <t>KHM 002003</t>
+          <t>O'R-SH 0661942</t>
         </is>
       </c>
       <c r="Q533" s="10" t="inlineStr"/>
       <c r="R533" s="10" t="inlineStr">
         <is>
-          <t>Shahrisabz shahridagi ishsiz va band bo'lmagan aholini kasb-hunarga o'qitish markazi</t>
+          <t>54-maktab</t>
         </is>
       </c>
       <c r="S533" s="11" t="inlineStr">
@@ -50119,67 +50135,63 @@
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>25-20</t>
+          <t>25-21</t>
         </is>
       </c>
       <c r="C534" s="3" t="inlineStr">
         <is>
-          <t>Xudoyorova Shahzoda</t>
+          <t>Xudoykulova Sadorat</t>
         </is>
       </c>
       <c r="D534" s="4" t="inlineStr"/>
-      <c r="E534" s="5" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
+      <c r="E534" s="5" t="inlineStr"/>
       <c r="F534" s="5" t="inlineStr"/>
       <c r="G534" s="5" t="inlineStr">
         <is>
-          <t>Shuxrat qizi</t>
+          <t>Muzurovna</t>
         </is>
       </c>
       <c r="H534" s="4" t="inlineStr">
         <is>
-          <t>Xudoyorova Shahzoda Shuxrat qizi</t>
+          <t>Xudoykulova Sadorat Muzurovna</t>
         </is>
       </c>
       <c r="I534" s="3" t="inlineStr"/>
       <c r="J534" s="5" t="inlineStr">
         <is>
-          <t>AD5989765</t>
+          <t>AB7071720</t>
         </is>
       </c>
       <c r="K534" s="2" t="inlineStr">
         <is>
-          <t>61909075590072</t>
+          <t>41712915680028</t>
         </is>
       </c>
       <c r="L534" s="5" t="inlineStr">
         <is>
-          <t>02.02.2024</t>
+          <t>28.06.2017</t>
         </is>
       </c>
       <c r="M534" s="5" t="inlineStr">
         <is>
-          <t>19.09.2007</t>
+          <t>17.12.1991</t>
         </is>
       </c>
       <c r="N534" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O534" s="4" t="inlineStr"/>
       <c r="P534" s="2" t="inlineStr">
         <is>
-          <t>UM 03295774</t>
+          <t>KHM 002003</t>
         </is>
       </c>
       <c r="Q534" s="4" t="inlineStr"/>
       <c r="R534" s="4" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>Shahrisabz shahridagi ishsiz va band bo'lmagan aholini kasb-hunarga o'qitish markazi</t>
         </is>
       </c>
       <c r="S534" s="5" t="inlineStr">
@@ -50207,89 +50219,81 @@
       </c>
       <c r="B535" s="8" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>25-20</t>
         </is>
       </c>
       <c r="C535" s="9" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona</t>
-        </is>
-      </c>
-      <c r="D535" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
+          <t>Xudoyorova Shahzoda</t>
+        </is>
+      </c>
+      <c r="D535" s="10" t="inlineStr"/>
       <c r="E535" s="11" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F535" s="11" t="inlineStr"/>
       <c r="G535" s="11" t="inlineStr">
         <is>
-          <t>Bahrom qizi</t>
+          <t>Shuxrat qizi</t>
         </is>
       </c>
       <c r="H535" s="10" t="inlineStr">
         <is>
-          <t>Xujamuratova Durdona Bahrom qizi</t>
+          <t>Xudoyorova Shahzoda Shuxrat qizi</t>
         </is>
       </c>
       <c r="I535" s="9" t="inlineStr"/>
       <c r="J535" s="11" t="inlineStr">
         <is>
-          <t>AE5954513</t>
+          <t>AD5989765</t>
         </is>
       </c>
       <c r="K535" s="8" t="inlineStr">
         <is>
-          <t>62204085720105</t>
+          <t>61909075590072</t>
         </is>
       </c>
       <c r="L535" s="11" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>02.02.2024</t>
         </is>
       </c>
       <c r="M535" s="11" t="inlineStr">
         <is>
-          <t>22.04.2008</t>
+          <t>19.09.2007</t>
         </is>
       </c>
       <c r="N535" s="11" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O535" s="10" t="inlineStr">
-        <is>
-          <t>Mavjud</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O535" s="10" t="inlineStr"/>
       <c r="P535" s="8" t="inlineStr">
         <is>
-          <t>UM 03717652</t>
+          <t>UM 03295774</t>
         </is>
       </c>
       <c r="Q535" s="10" t="inlineStr"/>
       <c r="R535" s="10" t="inlineStr">
         <is>
-          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>7-maktab</t>
         </is>
       </c>
       <c r="S535" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T535" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T535" s="11" t="inlineStr"/>
       <c r="U535" s="11" t="inlineStr"/>
-      <c r="V535" s="10" t="inlineStr"/>
+      <c r="V535" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
       <c r="W535" s="6" t="inlineStr"/>
       <c r="X535" s="7" t="inlineStr">
         <is>
@@ -50303,77 +50307,89 @@
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>25-19</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C536" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Asila</t>
-        </is>
-      </c>
-      <c r="D536" s="4" t="inlineStr"/>
-      <c r="E536" s="5" t="inlineStr"/>
+          <t>Xujamuratova Durdona</t>
+        </is>
+      </c>
+      <c r="D536" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E536" s="5" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
       <c r="F536" s="5" t="inlineStr"/>
       <c r="G536" s="5" t="inlineStr">
         <is>
-          <t>Ilhom qizi</t>
+          <t>Bahrom qizi</t>
         </is>
       </c>
       <c r="H536" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Asila Ilhom qizi</t>
+          <t>Xujamuratova Durdona Bahrom qizi</t>
         </is>
       </c>
       <c r="I536" s="3" t="inlineStr"/>
       <c r="J536" s="5" t="inlineStr">
         <is>
-          <t>AD4398661</t>
+          <t>AE5954513</t>
         </is>
       </c>
       <c r="K536" s="2" t="inlineStr">
         <is>
-          <t>60909065680045</t>
+          <t>62204085720105</t>
         </is>
       </c>
       <c r="L536" s="5" t="inlineStr">
         <is>
-          <t>24.08.2023</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="M536" s="5" t="inlineStr">
         <is>
-          <t>09.09.2006</t>
+          <t>22.04.2008</t>
         </is>
       </c>
       <c r="N536" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O536" s="4" t="inlineStr"/>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="O536" s="4" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
       <c r="P536" s="2" t="inlineStr">
         <is>
-          <t>UM 02150729</t>
+          <t>UM 03717652</t>
         </is>
       </c>
       <c r="Q536" s="4" t="inlineStr"/>
       <c r="R536" s="4" t="inlineStr">
         <is>
-          <t>28-maktab</t>
+          <t>19-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S536" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T536" s="5" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T536" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="U536" s="5" t="inlineStr"/>
-      <c r="V536" s="4" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
-        </is>
-      </c>
+      <c r="V536" s="4" t="inlineStr"/>
       <c r="W536" s="6" t="inlineStr"/>
       <c r="X536" s="7" t="inlineStr">
         <is>
@@ -50387,62 +50403,46 @@
       </c>
       <c r="B537" s="8" t="inlineStr">
         <is>
-          <t>26-03</t>
+          <t>25-19</t>
         </is>
       </c>
       <c r="C537" s="9" t="inlineStr">
         <is>
-          <t>Xurramova Lobar</t>
-        </is>
-      </c>
-      <c r="D537" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E537" s="11" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="F537" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Xurramova Asila</t>
+        </is>
+      </c>
+      <c r="D537" s="10" t="inlineStr"/>
+      <c r="E537" s="11" t="inlineStr"/>
+      <c r="F537" s="11" t="inlineStr"/>
       <c r="G537" s="11" t="inlineStr">
         <is>
-          <t>Ural qizi</t>
+          <t>Ilhom qizi</t>
         </is>
       </c>
       <c r="H537" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
-      <c r="I537" s="9" t="inlineStr">
-        <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
+          <t>Xurramova Asila Ilhom qizi</t>
+        </is>
+      </c>
+      <c r="I537" s="9" t="inlineStr"/>
       <c r="J537" s="11" t="inlineStr">
         <is>
-          <t>AE2656510</t>
+          <t>AD4398661</t>
         </is>
       </c>
       <c r="K537" s="8" t="inlineStr">
         <is>
-          <t>62508085680062</t>
+          <t>60909065680045</t>
         </is>
       </c>
       <c r="L537" s="11" t="inlineStr">
         <is>
-          <t>13.05.2025</t>
+          <t>24.08.2023</t>
         </is>
       </c>
       <c r="M537" s="11" t="inlineStr">
         <is>
-          <t>25.08.2008</t>
+          <t>09.09.2006</t>
         </is>
       </c>
       <c r="N537" s="11" t="inlineStr">
@@ -50450,47 +50450,31 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O537" s="10" t="inlineStr">
-        <is>
-          <t>Xurramova Lobar Ural qizi</t>
-        </is>
-      </c>
+      <c r="O537" s="10" t="inlineStr"/>
       <c r="P537" s="8" t="inlineStr">
         <is>
-          <t>UM 03728374</t>
-        </is>
-      </c>
-      <c r="Q537" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
-        </is>
-      </c>
+          <t>UM 02150729</t>
+        </is>
+      </c>
+      <c r="Q537" s="10" t="inlineStr"/>
       <c r="R537" s="10" t="inlineStr">
         <is>
-          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>28-maktab</t>
         </is>
       </c>
       <c r="S537" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T537" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U537" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V537" s="10" t="inlineStr"/>
-      <c r="W537" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T537" s="11" t="inlineStr"/>
+      <c r="U537" s="11" t="inlineStr"/>
+      <c r="V537" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W537" s="6" t="inlineStr"/>
       <c r="X537" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -50503,12 +50487,12 @@
       </c>
       <c r="B538" s="2" t="inlineStr">
         <is>
-          <t>26-07</t>
+          <t>26-03</t>
         </is>
       </c>
       <c r="C538" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Sabina</t>
+          <t>Xurramova Lobar</t>
         </is>
       </c>
       <c r="D538" s="4" t="inlineStr">
@@ -50518,56 +50502,72 @@
       </c>
       <c r="E538" s="5" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F538" s="5" t="inlineStr"/>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="F538" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G538" s="5" t="inlineStr">
         <is>
-          <t>Yuldosh qizi</t>
+          <t>Ural qizi</t>
         </is>
       </c>
       <c r="H538" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Sabina Yuldosh qizi</t>
-        </is>
-      </c>
-      <c r="I538" s="3" t="inlineStr"/>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
+      <c r="I538" s="3" t="inlineStr">
+        <is>
+          <t>Xurramova Lobar Ural qizi</t>
+        </is>
+      </c>
       <c r="J538" s="5" t="inlineStr">
         <is>
-          <t>AC3081523</t>
+          <t>AE2656510</t>
         </is>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
-          <t>60803048230011</t>
+          <t>62508085680062</t>
         </is>
       </c>
       <c r="L538" s="5" t="inlineStr">
         <is>
-          <t>16.10.2020</t>
+          <t>13.05.2025</t>
         </is>
       </c>
       <c r="M538" s="5" t="inlineStr">
         <is>
-          <t>08.03.2004</t>
-        </is>
-      </c>
-      <c r="N538" s="5" t="inlineStr"/>
+          <t>25.08.2008</t>
+        </is>
+      </c>
+      <c r="N538" s="5" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
       <c r="O538" s="4" t="inlineStr">
         <is>
-          <t>Mavjud</t>
+          <t>Xurramova Lobar Ural qizi</t>
         </is>
       </c>
       <c r="P538" s="2" t="inlineStr">
         <is>
-          <t>UM 1315230</t>
-        </is>
-      </c>
-      <c r="Q538" s="4" t="inlineStr"/>
+          <t>UM 03728374</t>
+        </is>
+      </c>
+      <c r="Q538" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4050114/3589063/4a1b655d-a1f1-4f07-8a33-02afae733dd7?preview=true</t>
+        </is>
+      </c>
       <c r="R538" s="4" t="inlineStr">
         <is>
-          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
+          <t>12-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S538" s="5" t="inlineStr">
@@ -50577,12 +50577,20 @@
       </c>
       <c r="T538" s="5" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U538" s="5" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U538" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V538" s="4" t="inlineStr"/>
-      <c r="W538" s="6" t="inlineStr"/>
+      <c r="W538" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X538" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -50595,12 +50603,12 @@
       </c>
       <c r="B539" s="8" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>26-07</t>
         </is>
       </c>
       <c r="C539" s="9" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza</t>
+          <t>Xurramova Sabina</t>
         </is>
       </c>
       <c r="D539" s="10" t="inlineStr">
@@ -50610,89 +50618,71 @@
       </c>
       <c r="E539" s="11" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F539" s="18" t="n">
-        <v>46204</v>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F539" s="11" t="inlineStr"/>
       <c r="G539" s="11" t="inlineStr">
         <is>
-          <t>Shuhrat qizi</t>
+          <t>Yuldosh qizi</t>
         </is>
       </c>
       <c r="H539" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
-      <c r="I539" s="9" t="inlineStr">
-        <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
-        </is>
-      </c>
+          <t>Xurramova Sabina Yuldosh qizi</t>
+        </is>
+      </c>
+      <c r="I539" s="9" t="inlineStr"/>
       <c r="J539" s="11" t="inlineStr">
         <is>
-          <t>AC1847101</t>
+          <t>AC3081523</t>
         </is>
       </c>
       <c r="K539" s="8" t="inlineStr">
         <is>
-          <t>60411015680031</t>
+          <t>60803048230011</t>
         </is>
       </c>
       <c r="L539" s="11" t="inlineStr">
         <is>
-          <t>24.04.2019</t>
+          <t>16.10.2020</t>
         </is>
       </c>
       <c r="M539" s="11" t="inlineStr">
         <is>
-          <t>04.11.2001</t>
-        </is>
-      </c>
-      <c r="N539" s="11" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
+          <t>08.03.2004</t>
+        </is>
+      </c>
+      <c r="N539" s="11" t="inlineStr"/>
       <c r="O539" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shahnoza Shuhrat qizi</t>
+          <t>Mavjud</t>
         </is>
       </c>
       <c r="P539" s="8" t="inlineStr">
         <is>
-          <t>UM 0084478</t>
+          <t>UM 1315230</t>
         </is>
       </c>
       <c r="Q539" s="10" t="inlineStr"/>
       <c r="R539" s="10" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
+          <t>4-sonli umumiy o’rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S539" s="11" t="inlineStr">
         <is>
-          <t>Attestat</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T539" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="U539" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U539" s="11" t="inlineStr"/>
       <c r="V539" s="10" t="inlineStr"/>
-      <c r="W539" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+      <c r="W539" s="6" t="inlineStr"/>
       <c r="X539" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -50710,7 +50700,7 @@
       </c>
       <c r="C540" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda</t>
+          <t>Xurramova Shahnoza</t>
         </is>
       </c>
       <c r="D540" s="4" t="inlineStr">
@@ -50720,13 +50710,11 @@
       </c>
       <c r="E540" s="5" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="F540" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F540" s="12" t="n">
+        <v>46204</v>
       </c>
       <c r="G540" s="5" t="inlineStr">
         <is>
@@ -50735,32 +50723,32 @@
       </c>
       <c r="H540" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="I540" s="3" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="J540" s="5" t="inlineStr">
         <is>
-          <t>AD4921163</t>
+          <t>AC1847101</t>
         </is>
       </c>
       <c r="K540" s="2" t="inlineStr">
         <is>
-          <t>63004075680030</t>
+          <t>60411015680031</t>
         </is>
       </c>
       <c r="L540" s="5" t="inlineStr">
         <is>
-          <t>20.10.2023</t>
+          <t>24.04.2019</t>
         </is>
       </c>
       <c r="M540" s="5" t="inlineStr">
         <is>
-          <t>30.04.2007</t>
+          <t>04.11.2001</t>
         </is>
       </c>
       <c r="N540" s="5" t="inlineStr">
@@ -50770,32 +50758,28 @@
       </c>
       <c r="O540" s="4" t="inlineStr">
         <is>
-          <t>Xurramova Shahrizoda Shuhrat qizi</t>
+          <t>Xurramova Shahnoza Shuhrat qizi</t>
         </is>
       </c>
       <c r="P540" s="2" t="inlineStr">
         <is>
-          <t>UM 02149677</t>
-        </is>
-      </c>
-      <c r="Q540" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0084478</t>
+        </is>
+      </c>
+      <c r="Q540" s="4" t="inlineStr"/>
       <c r="R540" s="4" t="inlineStr">
         <is>
-          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o‘rta ta’lim maktabi</t>
         </is>
       </c>
       <c r="S540" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
+          <t>Attestat</t>
         </is>
       </c>
       <c r="T540" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="U540" s="7" t="inlineStr">
@@ -50821,12 +50805,12 @@
       </c>
       <c r="B541" s="8" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C541" s="9" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya</t>
+          <t>Xurramova Shahrizoda</t>
         </is>
       </c>
       <c r="D541" s="10" t="inlineStr">
@@ -50836,7 +50820,7 @@
       </c>
       <c r="E541" s="11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F541" s="11" t="inlineStr">
@@ -50846,58 +50830,62 @@
       </c>
       <c r="G541" s="11" t="inlineStr">
         <is>
-          <t>Arol qizi</t>
+          <t>Shuhrat qizi</t>
         </is>
       </c>
       <c r="H541" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="I541" s="9" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="J541" s="11" t="inlineStr">
         <is>
-          <t>AC1967100</t>
+          <t>AD4921163</t>
         </is>
       </c>
       <c r="K541" s="8" t="inlineStr">
         <is>
-          <t>62704025590042</t>
+          <t>63004075680030</t>
         </is>
       </c>
       <c r="L541" s="11" t="inlineStr">
         <is>
-          <t>12.06.2019</t>
+          <t>20.10.2023</t>
         </is>
       </c>
       <c r="M541" s="11" t="inlineStr">
         <is>
-          <t>27.04.2002</t>
+          <t>30.04.2007</t>
         </is>
       </c>
       <c r="N541" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O541" s="10" t="inlineStr">
         <is>
-          <t>Xurramova Shodiya Arol qizi</t>
+          <t>Xurramova Shahrizoda Shuhrat qizi</t>
         </is>
       </c>
       <c r="P541" s="8" t="inlineStr">
         <is>
-          <t>UM 0438281</t>
-        </is>
-      </c>
-      <c r="Q541" s="10" t="inlineStr"/>
+          <t>UM 02149677</t>
+        </is>
+      </c>
+      <c r="Q541" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/1110983/1011765/4b67affc-8f51-4dc1-bb8c-08dc8aded5bd?preview=true</t>
+        </is>
+      </c>
       <c r="R541" s="10" t="inlineStr">
         <is>
-          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>3-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S541" s="11" t="inlineStr">
@@ -50907,7 +50895,7 @@
       </c>
       <c r="T541" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="U541" s="7" t="inlineStr">
@@ -50915,11 +50903,7 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V541" s="10" t="inlineStr">
-        <is>
-          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
-        </is>
-      </c>
+      <c r="V541" s="10" t="inlineStr"/>
       <c r="W541" s="13" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
@@ -50937,74 +50921,110 @@
       </c>
       <c r="B542" s="2" t="inlineStr">
         <is>
-          <t>Akademik ta'til olganlar</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C542" s="3" t="inlineStr">
         <is>
-          <t>Xusanboyeva Fotimaxon</t>
-        </is>
-      </c>
-      <c r="D542" s="4" t="inlineStr"/>
-      <c r="E542" s="5" t="inlineStr"/>
-      <c r="F542" s="5" t="inlineStr"/>
+          <t>Xurramova Shodiya</t>
+        </is>
+      </c>
+      <c r="D542" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E542" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F542" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G542" s="5" t="inlineStr">
         <is>
-          <t>Baxtiyor qizi</t>
+          <t>Arol qizi</t>
         </is>
       </c>
       <c r="H542" s="4" t="inlineStr">
         <is>
-          <t>Xusanboyeva Fotimaxon Baxtiyor qizi</t>
-        </is>
-      </c>
-      <c r="I542" s="3" t="inlineStr"/>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
+      <c r="I542" s="3" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
       <c r="J542" s="5" t="inlineStr">
         <is>
-          <t>AD4614901</t>
+          <t>AC1967100</t>
         </is>
       </c>
       <c r="K542" s="2" t="inlineStr">
         <is>
-          <t>60805045930053</t>
+          <t>62704025590042</t>
         </is>
       </c>
       <c r="L542" s="5" t="inlineStr">
         <is>
-          <t>15.09.2023</t>
+          <t>12.06.2019</t>
         </is>
       </c>
       <c r="M542" s="5" t="inlineStr">
         <is>
-          <t>08.05.2004</t>
-        </is>
-      </c>
-      <c r="N542" s="5" t="inlineStr"/>
-      <c r="O542" s="4" t="inlineStr"/>
+          <t>27.04.2002</t>
+        </is>
+      </c>
+      <c r="N542" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O542" s="4" t="inlineStr">
+        <is>
+          <t>Xurramova Shodiya Arol qizi</t>
+        </is>
+      </c>
       <c r="P542" s="2" t="inlineStr">
         <is>
-          <t>UM 1347858</t>
+          <t>UM 0438281</t>
         </is>
       </c>
       <c r="Q542" s="4" t="inlineStr"/>
       <c r="R542" s="4" t="inlineStr">
         <is>
-          <t>22-maktab</t>
+          <t>29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S542" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T542" s="5" t="inlineStr"/>
-      <c r="U542" s="5" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T542" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U542" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V542" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
-        </is>
-      </c>
-      <c r="W542" s="6" t="inlineStr"/>
+          <t>Fayl qo'lda tasdiqlandi: Xurramova Shodiya.docx (#02). Pasport AC1967100 va attestat UM 0438281 rasmlari bilan to'liq mos.</t>
+        </is>
+      </c>
+      <c r="W542" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X542" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -51017,114 +51037,74 @@
       </c>
       <c r="B543" s="8" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>Akademik ta'til olganlar</t>
         </is>
       </c>
       <c r="C543" s="9" t="inlineStr">
         <is>
-          <t>Xusanova Aziza</t>
-        </is>
-      </c>
-      <c r="D543" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E543" s="11" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="F543" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Xusanboyeva Fotimaxon</t>
+        </is>
+      </c>
+      <c r="D543" s="10" t="inlineStr"/>
+      <c r="E543" s="11" t="inlineStr"/>
+      <c r="F543" s="11" t="inlineStr"/>
       <c r="G543" s="11" t="inlineStr">
         <is>
-          <t>Fazliddin qizi</t>
+          <t>Baxtiyor qizi</t>
         </is>
       </c>
       <c r="H543" s="10" t="inlineStr">
         <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
-        </is>
-      </c>
-      <c r="I543" s="9" t="inlineStr">
-        <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
-        </is>
-      </c>
+          <t>Xusanboyeva Fotimaxon Baxtiyor qizi</t>
+        </is>
+      </c>
+      <c r="I543" s="9" t="inlineStr"/>
       <c r="J543" s="11" t="inlineStr">
         <is>
-          <t>AE5015467</t>
+          <t>AD4614901</t>
         </is>
       </c>
       <c r="K543" s="8" t="inlineStr">
         <is>
-          <t>60110085590092</t>
+          <t>60805045930053</t>
         </is>
       </c>
       <c r="L543" s="11" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>15.09.2023</t>
         </is>
       </c>
       <c r="M543" s="11" t="inlineStr">
         <is>
-          <t>01.10.2008</t>
-        </is>
-      </c>
-      <c r="N543" s="11" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O543" s="10" t="inlineStr">
-        <is>
-          <t>Xusanova Aziza Fazliddin qizi</t>
-        </is>
-      </c>
+          <t>08.05.2004</t>
+        </is>
+      </c>
+      <c r="N543" s="11" t="inlineStr"/>
+      <c r="O543" s="10" t="inlineStr"/>
       <c r="P543" s="8" t="inlineStr">
         <is>
-          <t>UM 03753649</t>
-        </is>
-      </c>
-      <c r="Q543" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
-        </is>
-      </c>
+          <t>UM 1347858</t>
+        </is>
+      </c>
+      <c r="Q543" s="10" t="inlineStr"/>
       <c r="R543" s="10" t="inlineStr">
         <is>
-          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>22-maktab</t>
         </is>
       </c>
       <c r="S543" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T543" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U543" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T543" s="11" t="inlineStr"/>
+      <c r="U543" s="11" t="inlineStr"/>
       <c r="V543" s="10" t="inlineStr">
         <is>
-          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
-        </is>
-      </c>
-      <c r="W543" s="13" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-23</t>
+        </is>
+      </c>
+      <c r="W543" s="6" t="inlineStr"/>
       <c r="X543" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -51137,78 +51117,114 @@
       </c>
       <c r="B544" s="2" t="inlineStr">
         <is>
-          <t>25-16</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C544" s="3" t="inlineStr">
         <is>
-          <t>Xushvaqtova Muxlisa</t>
-        </is>
-      </c>
-      <c r="D544" s="4" t="inlineStr"/>
-      <c r="E544" s="5" t="inlineStr"/>
-      <c r="F544" s="5" t="inlineStr"/>
+          <t>Xusanova Aziza</t>
+        </is>
+      </c>
+      <c r="D544" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E544" s="5" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="F544" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G544" s="5" t="inlineStr">
         <is>
-          <t>Olim qizi</t>
+          <t>Fazliddin qizi</t>
         </is>
       </c>
       <c r="H544" s="4" t="inlineStr">
         <is>
-          <t>Xushvaqtova Muxlisa Olim qizi</t>
-        </is>
-      </c>
-      <c r="I544" s="3" t="inlineStr"/>
+          <t>Xusanova Aziza Fazliddin qizi</t>
+        </is>
+      </c>
+      <c r="I544" s="3" t="inlineStr">
+        <is>
+          <t>Xusanova Aziza Fazliddin qizi</t>
+        </is>
+      </c>
       <c r="J544" s="5" t="inlineStr">
         <is>
-          <t>AD2966760</t>
+          <t>AE5015467</t>
         </is>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
-          <t>62103075730017</t>
+          <t>60110085590092</t>
         </is>
       </c>
       <c r="L544" s="5" t="inlineStr">
         <is>
-          <t>06.04.2023</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="M544" s="5" t="inlineStr">
         <is>
-          <t>21.03.2007</t>
+          <t>01.10.2008</t>
         </is>
       </c>
       <c r="N544" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
-        </is>
-      </c>
-      <c r="O544" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O544" s="4" t="inlineStr">
+        <is>
+          <t>Xusanova Aziza Fazliddin qizi</t>
+        </is>
+      </c>
       <c r="P544" s="2" t="inlineStr">
         <is>
-          <t>UM 03263388</t>
-        </is>
-      </c>
-      <c r="Q544" s="4" t="inlineStr"/>
+          <t>UM 03753649</t>
+        </is>
+      </c>
+      <c r="Q544" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3862927/3632621/f304426a-09be-4ffa-98ef-fde425a55514?preview=true</t>
+        </is>
+      </c>
       <c r="R544" s="4" t="inlineStr">
         <is>
-          <t>21-maktab</t>
+          <t>15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S544" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T544" s="5" t="inlineStr"/>
-      <c r="U544" s="5" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T544" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U544" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V544" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
-        </is>
-      </c>
-      <c r="W544" s="6" t="inlineStr"/>
+          <t>PINFL ID-karta MRZ dan tuzatildi (edi: 60110085590028).</t>
+        </is>
+      </c>
+      <c r="W544" s="13" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X544" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -51221,106 +51237,78 @@
       </c>
       <c r="B545" s="8" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>25-16</t>
         </is>
       </c>
       <c r="C545" s="9" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam</t>
+          <t>Xushvaqtova Muxlisa</t>
         </is>
       </c>
       <c r="D545" s="10" t="inlineStr"/>
-      <c r="E545" s="11" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="F545" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E545" s="11" t="inlineStr"/>
+      <c r="F545" s="11" t="inlineStr"/>
       <c r="G545" s="11" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Olim qizi</t>
         </is>
       </c>
       <c r="H545" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
-        </is>
-      </c>
-      <c r="I545" s="9" t="inlineStr">
-        <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
-        </is>
-      </c>
+          <t>Xushvaqtova Muxlisa Olim qizi</t>
+        </is>
+      </c>
+      <c r="I545" s="9" t="inlineStr"/>
       <c r="J545" s="11" t="inlineStr">
         <is>
-          <t>AE4629898</t>
+          <t>AD2966760</t>
         </is>
       </c>
       <c r="K545" s="8" t="inlineStr">
         <is>
-          <t>62802085680012</t>
+          <t>62103075730017</t>
         </is>
       </c>
       <c r="L545" s="11" t="inlineStr">
         <is>
-          <t>15.10.2025</t>
+          <t>06.04.2023</t>
         </is>
       </c>
       <c r="M545" s="11" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>21.03.2007</t>
         </is>
       </c>
       <c r="N545" s="11" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O545" s="10" t="inlineStr">
-        <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
-        </is>
-      </c>
+          <t>Yakkabog' tumani</t>
+        </is>
+      </c>
+      <c r="O545" s="10" t="inlineStr"/>
       <c r="P545" s="8" t="inlineStr">
         <is>
-          <t>UM 03729356</t>
-        </is>
-      </c>
-      <c r="Q545" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03263388</t>
+        </is>
+      </c>
+      <c r="Q545" s="10" t="inlineStr"/>
       <c r="R545" s="10" t="inlineStr">
         <is>
-          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>21-maktab</t>
         </is>
       </c>
       <c r="S545" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T545" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U545" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V545" s="10" t="inlineStr"/>
-      <c r="W545" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T545" s="11" t="inlineStr"/>
+      <c r="U545" s="11" t="inlineStr"/>
+      <c r="V545" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W545" s="6" t="inlineStr"/>
       <c r="X545" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -51333,78 +51321,106 @@
       </c>
       <c r="B546" s="2" t="inlineStr">
         <is>
-          <t>25-16</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C546" s="3" t="inlineStr">
         <is>
-          <t>Yarasheva Ruxshonaoy</t>
+          <t>Yahyomurodova Gulsanam</t>
         </is>
       </c>
       <c r="D546" s="4" t="inlineStr"/>
-      <c r="E546" s="5" t="inlineStr"/>
-      <c r="F546" s="5" t="inlineStr"/>
+      <c r="E546" s="5" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="F546" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G546" s="5" t="inlineStr">
         <is>
-          <t>Uchqun qizi</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H546" s="4" t="inlineStr">
         <is>
-          <t>Yarasheva Ruxshonaoy Uchqun qizi</t>
-        </is>
-      </c>
-      <c r="I546" s="3" t="inlineStr"/>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+        </is>
+      </c>
+      <c r="I546" s="3" t="inlineStr">
+        <is>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+        </is>
+      </c>
       <c r="J546" s="5" t="inlineStr">
         <is>
-          <t>AD5460000</t>
+          <t>AE4629898</t>
         </is>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
-          <t>61010065590076</t>
+          <t>62802085680012</t>
         </is>
       </c>
       <c r="L546" s="5" t="inlineStr">
         <is>
-          <t>18.12.2023</t>
+          <t>15.10.2025</t>
         </is>
       </c>
       <c r="M546" s="5" t="inlineStr">
         <is>
-          <t>10.10.2006</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="N546" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O546" s="4" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O546" s="4" t="inlineStr">
+        <is>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+        </is>
+      </c>
       <c r="P546" s="2" t="inlineStr">
         <is>
-          <t>UM 02173517</t>
-        </is>
-      </c>
-      <c r="Q546" s="4" t="inlineStr"/>
+          <t>UM 03729356</t>
+        </is>
+      </c>
+      <c r="Q546" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/4101966/3670372/d6892206-ed4f-4765-b023-063702028ca9?preview=true</t>
+        </is>
+      </c>
       <c r="R546" s="4" t="inlineStr">
         <is>
-          <t>17-maktab</t>
+          <t>46-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S546" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T546" s="5" t="inlineStr"/>
-      <c r="U546" s="5" t="inlineStr"/>
-      <c r="V546" s="4" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
-        </is>
-      </c>
-      <c r="W546" s="6" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T546" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U546" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V546" s="4" t="inlineStr"/>
+      <c r="W546" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X546" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -51417,12 +51433,12 @@
       </c>
       <c r="B547" s="8" t="inlineStr">
         <is>
-          <t>Talabalar safidan chiqarilganlar</t>
+          <t>25-16</t>
         </is>
       </c>
       <c r="C547" s="9" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna</t>
+          <t>Yarasheva Ruxshonaoy</t>
         </is>
       </c>
       <c r="D547" s="10" t="inlineStr"/>
@@ -51430,31 +51446,35 @@
       <c r="F547" s="11" t="inlineStr"/>
       <c r="G547" s="11" t="inlineStr">
         <is>
-          <t>Hushvaqt qizi</t>
+          <t>Uchqun qizi</t>
         </is>
       </c>
       <c r="H547" s="10" t="inlineStr">
         <is>
-          <t>Yoqubova Maftuna Hushvaqt qizi</t>
+          <t>Yarasheva Ruxshonaoy Uchqun qizi</t>
         </is>
       </c>
       <c r="I547" s="9" t="inlineStr"/>
       <c r="J547" s="11" t="inlineStr">
         <is>
-          <t>AE2747402</t>
+          <t>AD5460000</t>
         </is>
       </c>
       <c r="K547" s="8" t="inlineStr">
         <is>
-          <t>40312902560107</t>
+          <t>61010065590076</t>
         </is>
       </c>
       <c r="L547" s="11" t="inlineStr">
         <is>
-          <t>20,05,2025</t>
-        </is>
-      </c>
-      <c r="M547" s="11" t="inlineStr"/>
+          <t>18.12.2023</t>
+        </is>
+      </c>
+      <c r="M547" s="11" t="inlineStr">
+        <is>
+          <t>10.10.2006</t>
+        </is>
+      </c>
       <c r="N547" s="11" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
@@ -51463,25 +51483,25 @@
       <c r="O547" s="10" t="inlineStr"/>
       <c r="P547" s="8" t="inlineStr">
         <is>
-          <t>K 1234480</t>
+          <t>UM 02173517</t>
         </is>
       </c>
       <c r="Q547" s="10" t="inlineStr"/>
       <c r="R547" s="10" t="inlineStr">
         <is>
-          <t>Miroqi sport pedagogika kolleji</t>
+          <t>17-maktab</t>
         </is>
       </c>
       <c r="S547" s="11" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T547" s="11" t="inlineStr"/>
       <c r="U547" s="11" t="inlineStr"/>
       <c r="V547" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 2-kurs</t>
         </is>
       </c>
       <c r="W547" s="6" t="inlineStr"/>
@@ -51497,110 +51517,74 @@
       </c>
       <c r="B548" s="2" t="inlineStr">
         <is>
-          <t>26-02</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C548" s="3" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo</t>
-        </is>
-      </c>
-      <c r="D548" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E548" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="F548" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Yoqubova Maftuna</t>
+        </is>
+      </c>
+      <c r="D548" s="4" t="inlineStr"/>
+      <c r="E548" s="5" t="inlineStr"/>
+      <c r="F548" s="5" t="inlineStr"/>
       <c r="G548" s="5" t="inlineStr">
         <is>
-          <t>Xusan qizi</t>
+          <t>Hushvaqt qizi</t>
         </is>
       </c>
       <c r="H548" s="4" t="inlineStr">
         <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
-      <c r="I548" s="3" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
+          <t>Yoqubova Maftuna Hushvaqt qizi</t>
+        </is>
+      </c>
+      <c r="I548" s="3" t="inlineStr"/>
       <c r="J548" s="5" t="inlineStr">
         <is>
-          <t>AB9239333</t>
+          <t>AE2747402</t>
         </is>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
-          <t>42207935680042</t>
+          <t>40312902560107</t>
         </is>
       </c>
       <c r="L548" s="5" t="inlineStr">
         <is>
-          <t>09.04.2018</t>
-        </is>
-      </c>
-      <c r="M548" s="5" t="inlineStr">
-        <is>
-          <t>22.07.1993</t>
-        </is>
-      </c>
+          <t>20,05,2025</t>
+        </is>
+      </c>
+      <c r="M548" s="5" t="inlineStr"/>
       <c r="N548" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O548" s="4" t="inlineStr">
-        <is>
-          <t>Yorboboyeva Mahliyo Xusan qizi</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O548" s="4" t="inlineStr"/>
       <c r="P548" s="2" t="inlineStr">
         <is>
-          <t>UM 03524597</t>
-        </is>
-      </c>
-      <c r="Q548" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
-        </is>
-      </c>
+          <t>K 1234480</t>
+        </is>
+      </c>
+      <c r="Q548" s="4" t="inlineStr"/>
       <c r="R548" s="4" t="inlineStr">
         <is>
-          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Miroqi sport pedagogika kolleji</t>
         </is>
       </c>
       <c r="S548" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T548" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U548" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V548" s="4" t="inlineStr"/>
-      <c r="W548" s="13" t="inlineStr">
-        <is>
-          <t>Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T548" s="5" t="inlineStr"/>
+      <c r="U548" s="5" t="inlineStr"/>
+      <c r="V548" s="4" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W548" s="6" t="inlineStr"/>
       <c r="X548" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -51613,82 +51597,110 @@
       </c>
       <c r="B549" s="8" t="inlineStr">
         <is>
-          <t>25-21</t>
+          <t>26-02</t>
         </is>
       </c>
       <c r="C549" s="9" t="inlineStr">
         <is>
-          <t>Yorboboyeva Shaxzoda</t>
-        </is>
-      </c>
-      <c r="D549" s="10" t="inlineStr"/>
+          <t>Yorboboyeva Mahliyo</t>
+        </is>
+      </c>
+      <c r="D549" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
       <c r="E549" s="11" t="inlineStr">
         <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="F549" s="11" t="inlineStr"/>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F549" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G549" s="11" t="inlineStr">
         <is>
-          <t>Zokirjon qizi</t>
+          <t>Xusan qizi</t>
         </is>
       </c>
       <c r="H549" s="10" t="inlineStr">
         <is>
-          <t>Yorboboyeva Shaxzoda Zokirjon qizi</t>
-        </is>
-      </c>
-      <c r="I549" s="9" t="inlineStr"/>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+        </is>
+      </c>
+      <c r="I549" s="9" t="inlineStr">
+        <is>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+        </is>
+      </c>
       <c r="J549" s="11" t="inlineStr">
         <is>
-          <t>AD9750298</t>
+          <t>AB9239333</t>
         </is>
       </c>
       <c r="K549" s="8" t="inlineStr">
         <is>
-          <t>63005085590050</t>
+          <t>42207935680042</t>
         </is>
       </c>
       <c r="L549" s="11" t="inlineStr">
         <is>
-          <t>10.12.2024</t>
+          <t>09.04.2018</t>
         </is>
       </c>
       <c r="M549" s="11" t="inlineStr">
         <is>
-          <t>30.05.2008</t>
+          <t>22.07.1993</t>
         </is>
       </c>
       <c r="N549" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="O549" s="10" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O549" s="10" t="inlineStr">
+        <is>
+          <t>Yorboboyeva Mahliyo Xusan qizi</t>
+        </is>
+      </c>
       <c r="P549" s="8" t="inlineStr">
         <is>
-          <t>UM 03296187</t>
-        </is>
-      </c>
-      <c r="Q549" s="10" t="inlineStr"/>
+          <t>UM 03524597</t>
+        </is>
+      </c>
+      <c r="Q549" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3351696/3151125/7ae6a3dc-9024-4738-9150-7aea65c95559?preview=true</t>
+        </is>
+      </c>
       <c r="R549" s="10" t="inlineStr">
         <is>
-          <t>14-maktab</t>
+          <t>45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S549" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T549" s="11" t="inlineStr"/>
-      <c r="U549" s="11" t="inlineStr"/>
-      <c r="V549" s="10" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
-        </is>
-      </c>
-      <c r="W549" s="6" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T549" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U549" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V549" s="10" t="inlineStr"/>
+      <c r="W549" s="13" t="inlineStr">
+        <is>
+          <t>Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X549" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -51701,44 +51713,52 @@
       </c>
       <c r="B550" s="2" t="inlineStr">
         <is>
-          <t>Talabalar safidan chiqarilganlar</t>
+          <t>25-21</t>
         </is>
       </c>
       <c r="C550" s="3" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda</t>
+          <t>Yorboboyeva Shaxzoda</t>
         </is>
       </c>
       <c r="D550" s="4" t="inlineStr"/>
-      <c r="E550" s="5" t="inlineStr"/>
+      <c r="E550" s="5" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
       <c r="F550" s="5" t="inlineStr"/>
       <c r="G550" s="5" t="inlineStr">
         <is>
-          <t>Hasanovna</t>
+          <t>Zokirjon qizi</t>
         </is>
       </c>
       <c r="H550" s="4" t="inlineStr">
         <is>
-          <t>Yuldosheva Iroda Hasanovna</t>
+          <t>Yorboboyeva Shaxzoda Zokirjon qizi</t>
         </is>
       </c>
       <c r="I550" s="3" t="inlineStr"/>
       <c r="J550" s="5" t="inlineStr">
         <is>
-          <t>AB7535578</t>
+          <t>AD9750298</t>
         </is>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
-          <t>40108945590034</t>
+          <t>63005085590050</t>
         </is>
       </c>
       <c r="L550" s="5" t="inlineStr">
         <is>
-          <t>22,08,2017</t>
-        </is>
-      </c>
-      <c r="M550" s="5" t="inlineStr"/>
+          <t>10.12.2024</t>
+        </is>
+      </c>
+      <c r="M550" s="5" t="inlineStr">
+        <is>
+          <t>30.05.2008</t>
+        </is>
+      </c>
       <c r="N550" s="5" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
@@ -51747,25 +51767,25 @@
       <c r="O550" s="4" t="inlineStr"/>
       <c r="P550" s="2" t="inlineStr">
         <is>
-          <t>K 2404534</t>
+          <t>UM 03296187</t>
         </is>
       </c>
       <c r="Q550" s="4" t="inlineStr"/>
       <c r="R550" s="4" t="inlineStr">
         <is>
-          <t>Shahrisabz pedagogika kolleji</t>
+          <t>14-maktab</t>
         </is>
       </c>
       <c r="S550" s="5" t="inlineStr">
         <is>
-          <t>Kollej</t>
+          <t>Umumiy o'rta maktab</t>
         </is>
       </c>
       <c r="T550" s="5" t="inlineStr"/>
       <c r="U550" s="5" t="inlineStr"/>
       <c r="V550" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 2-kurs</t>
         </is>
       </c>
       <c r="W550" s="6" t="inlineStr"/>
@@ -51781,110 +51801,74 @@
       </c>
       <c r="B551" s="8" t="inlineStr">
         <is>
-          <t>26-05</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C551" s="9" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona</t>
-        </is>
-      </c>
-      <c r="D551" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E551" s="11" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="F551" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Yuldosheva Iroda</t>
+        </is>
+      </c>
+      <c r="D551" s="10" t="inlineStr"/>
+      <c r="E551" s="11" t="inlineStr"/>
+      <c r="F551" s="11" t="inlineStr"/>
       <c r="G551" s="11" t="inlineStr">
         <is>
-          <t>Xabibullo qizi</t>
+          <t>Hasanovna</t>
         </is>
       </c>
       <c r="H551" s="10" t="inlineStr">
         <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
-        </is>
-      </c>
-      <c r="I551" s="9" t="inlineStr">
-        <is>
-          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
-        </is>
-      </c>
+          <t>Yuldosheva Iroda Hasanovna</t>
+        </is>
+      </c>
+      <c r="I551" s="9" t="inlineStr"/>
       <c r="J551" s="11" t="inlineStr">
         <is>
-          <t>AE1419035</t>
+          <t>AB7535578</t>
         </is>
       </c>
       <c r="K551" s="8" t="inlineStr">
         <is>
-          <t>61309085590066</t>
+          <t>40108945590034</t>
         </is>
       </c>
       <c r="L551" s="11" t="inlineStr">
         <is>
-          <t>29.01.2025</t>
-        </is>
-      </c>
-      <c r="M551" s="11" t="inlineStr">
-        <is>
-          <t>13.09.2008</t>
-        </is>
-      </c>
+          <t>22,08,2017</t>
+        </is>
+      </c>
+      <c r="M551" s="11" t="inlineStr"/>
       <c r="N551" s="11" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O551" s="10" t="inlineStr">
-        <is>
-          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
-        </is>
-      </c>
+      <c r="O551" s="10" t="inlineStr"/>
       <c r="P551" s="8" t="inlineStr">
         <is>
-          <t>PT 0339260</t>
+          <t>K 2404534</t>
         </is>
       </c>
       <c r="Q551" s="10" t="inlineStr"/>
       <c r="R551" s="10" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar 2-son texnikumi</t>
+          <t>Shahrisabz pedagogika kolleji</t>
         </is>
       </c>
       <c r="S551" s="11" t="inlineStr">
         <is>
-          <t>Diplom</t>
-        </is>
-      </c>
-      <c r="T551" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U551" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
+          <t>Kollej</t>
+        </is>
+      </c>
+      <c r="T551" s="11" t="inlineStr"/>
+      <c r="U551" s="11" t="inlineStr"/>
       <c r="V551" s="10" t="inlineStr">
         <is>
-          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
-        </is>
-      </c>
-      <c r="W551" s="16" t="inlineStr">
-        <is>
-          <t>Pasport: TRANSLIT</t>
-        </is>
-      </c>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W551" s="6" t="inlineStr"/>
       <c r="X551" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -51897,78 +51881,110 @@
       </c>
       <c r="B552" s="2" t="inlineStr">
         <is>
-          <t>24-12</t>
+          <t>26-05</t>
         </is>
       </c>
       <c r="C552" s="3" t="inlineStr">
         <is>
-          <t>Yuldoshova Diyora</t>
-        </is>
-      </c>
-      <c r="D552" s="4" t="inlineStr"/>
-      <c r="E552" s="5" t="inlineStr"/>
-      <c r="F552" s="5" t="inlineStr"/>
+          <t>Yuldosheva Ruhshona</t>
+        </is>
+      </c>
+      <c r="D552" s="4" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E552" s="5" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F552" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G552" s="5" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Xabibullo qizi</t>
         </is>
       </c>
       <c r="H552" s="4" t="inlineStr">
         <is>
-          <t>Yuldoshova Diyora Sherzod qizi</t>
-        </is>
-      </c>
-      <c r="I552" s="3" t="inlineStr"/>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+        </is>
+      </c>
+      <c r="I552" s="3" t="inlineStr">
+        <is>
+          <t>Yuldosheva Ruhshona Xabibullo qizi</t>
+        </is>
+      </c>
       <c r="J552" s="5" t="inlineStr">
         <is>
-          <t>AD5277554</t>
+          <t>AE1419035</t>
         </is>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
-          <t>60106065720092</t>
+          <t>61309085590066</t>
         </is>
       </c>
       <c r="L552" s="5" t="inlineStr">
         <is>
-          <t>30.11.2023</t>
+          <t>29.01.2025</t>
         </is>
       </c>
       <c r="M552" s="5" t="inlineStr">
         <is>
-          <t>01.06.2006</t>
+          <t>13.09.2008</t>
         </is>
       </c>
       <c r="N552" s="5" t="inlineStr">
         <is>
-          <t>Chiroqchi tumani</t>
-        </is>
-      </c>
-      <c r="O552" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O552" s="4" t="inlineStr">
+        <is>
+          <t>Yo'ldosheva Ruxshona Xabibullo qizi</t>
+        </is>
+      </c>
       <c r="P552" s="2" t="inlineStr">
         <is>
-          <t>UM 02139583</t>
+          <t>PT 0339260</t>
         </is>
       </c>
       <c r="Q552" s="4" t="inlineStr"/>
       <c r="R552" s="4" t="inlineStr">
         <is>
-          <t>14-maktab</t>
+          <t>Shahrisabz shahar 2-son texnikumi</t>
         </is>
       </c>
       <c r="S552" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T552" s="5" t="inlineStr"/>
-      <c r="U552" s="5" t="inlineStr"/>
+          <t>Diplom</t>
+        </is>
+      </c>
+      <c r="T552" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U552" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V552" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 3-kurs</t>
-        </is>
-      </c>
-      <c r="W552" s="6" t="inlineStr"/>
+          <t>TEKSHIRILSIN: imlo farqi — ID-karta MRZ: 'YULDOSHEVA RUHSHONA' | bazada: 'Yo'ldosheva Ruxshona'</t>
+        </is>
+      </c>
+      <c r="W552" s="16" t="inlineStr">
+        <is>
+          <t>Pasport: TRANSLIT</t>
+        </is>
+      </c>
       <c r="X552" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -51981,12 +51997,12 @@
       </c>
       <c r="B553" s="8" t="inlineStr">
         <is>
-          <t>24-16</t>
+          <t>24-12</t>
         </is>
       </c>
       <c r="C553" s="9" t="inlineStr">
         <is>
-          <t>Yunusova Qurbonoy</t>
+          <t>Yuldoshova Diyora</t>
         </is>
       </c>
       <c r="D553" s="10" t="inlineStr"/>
@@ -51994,46 +52010,50 @@
       <c r="F553" s="11" t="inlineStr"/>
       <c r="G553" s="11" t="inlineStr">
         <is>
-          <t>Kamol qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H553" s="10" t="inlineStr">
         <is>
-          <t>Yunusova Qurbonoy Kamol qizi</t>
+          <t>Yuldoshova Diyora Sherzod qizi</t>
         </is>
       </c>
       <c r="I553" s="9" t="inlineStr"/>
       <c r="J553" s="11" t="inlineStr">
         <is>
-          <t>AC3197177</t>
+          <t>AD5277554</t>
         </is>
       </c>
       <c r="K553" s="8" t="inlineStr">
         <is>
-          <t>60102048230011</t>
+          <t>60106065720092</t>
         </is>
       </c>
       <c r="L553" s="11" t="inlineStr">
         <is>
-          <t>11.12.2020</t>
+          <t>30.11.2023</t>
         </is>
       </c>
       <c r="M553" s="11" t="inlineStr">
         <is>
-          <t>01.02.2004</t>
-        </is>
-      </c>
-      <c r="N553" s="11" t="inlineStr"/>
+          <t>01.06.2006</t>
+        </is>
+      </c>
+      <c r="N553" s="11" t="inlineStr">
+        <is>
+          <t>Chiroqchi tumani</t>
+        </is>
+      </c>
       <c r="O553" s="10" t="inlineStr"/>
       <c r="P553" s="8" t="inlineStr">
         <is>
-          <t>UM 0887275</t>
+          <t>UM 02139583</t>
         </is>
       </c>
       <c r="Q553" s="10" t="inlineStr"/>
       <c r="R553" s="10" t="inlineStr">
         <is>
-          <t>48-maktab</t>
+          <t>14-maktab</t>
         </is>
       </c>
       <c r="S553" s="11" t="inlineStr">
@@ -52045,7 +52065,7 @@
       <c r="U553" s="11" t="inlineStr"/>
       <c r="V553" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
+          <t>2025-2026 kontingenti: 3-kurs</t>
         </is>
       </c>
       <c r="W553" s="6" t="inlineStr"/>
@@ -52061,12 +52081,12 @@
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>Akademik ta'til olganlar</t>
+          <t>24-16</t>
         </is>
       </c>
       <c r="C554" s="3" t="inlineStr">
         <is>
-          <t>Yusupova Asila</t>
+          <t>Yunusova Qurbonoy</t>
         </is>
       </c>
       <c r="D554" s="4" t="inlineStr"/>
@@ -52074,50 +52094,46 @@
       <c r="F554" s="5" t="inlineStr"/>
       <c r="G554" s="5" t="inlineStr">
         <is>
-          <t>Iskandar qizi</t>
+          <t>Kamol qizi</t>
         </is>
       </c>
       <c r="H554" s="4" t="inlineStr">
         <is>
-          <t>Yusupova Asila Iskandar qizi</t>
+          <t>Yunusova Qurbonoy Kamol qizi</t>
         </is>
       </c>
       <c r="I554" s="3" t="inlineStr"/>
       <c r="J554" s="5" t="inlineStr">
         <is>
-          <t>AD0311873</t>
+          <t>AC3197177</t>
         </is>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
-          <t>61007015680048</t>
+          <t>60102048230011</t>
         </is>
       </c>
       <c r="L554" s="5" t="inlineStr">
         <is>
-          <t>13.04.2021</t>
+          <t>11.12.2020</t>
         </is>
       </c>
       <c r="M554" s="5" t="inlineStr">
         <is>
-          <t>10.07.2001</t>
-        </is>
-      </c>
-      <c r="N554" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
+          <t>01.02.2004</t>
+        </is>
+      </c>
+      <c r="N554" s="5" t="inlineStr"/>
       <c r="O554" s="4" t="inlineStr"/>
       <c r="P554" s="2" t="inlineStr">
         <is>
-          <t>UM 0085864</t>
+          <t>UM 0887275</t>
         </is>
       </c>
       <c r="Q554" s="4" t="inlineStr"/>
       <c r="R554" s="4" t="inlineStr">
         <is>
-          <t>51-maktab</t>
+          <t>48-maktab</t>
         </is>
       </c>
       <c r="S554" s="5" t="inlineStr">
@@ -52129,7 +52145,7 @@
       <c r="U554" s="5" t="inlineStr"/>
       <c r="V554" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
+          <t>2025-2026 kontingenti: 2-kurs</t>
         </is>
       </c>
       <c r="W554" s="6" t="inlineStr"/>
@@ -52145,50 +52161,46 @@
       </c>
       <c r="B555" s="8" t="inlineStr">
         <is>
-          <t>25-19</t>
+          <t>Akademik ta'til olganlar</t>
         </is>
       </c>
       <c r="C555" s="9" t="inlineStr">
         <is>
-          <t>Yusupova Dilnura</t>
+          <t>Yusupova Asila</t>
         </is>
       </c>
       <c r="D555" s="10" t="inlineStr"/>
-      <c r="E555" s="11" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
+      <c r="E555" s="11" t="inlineStr"/>
       <c r="F555" s="11" t="inlineStr"/>
       <c r="G555" s="11" t="inlineStr">
         <is>
-          <t>Nuriddin qizi</t>
+          <t>Iskandar qizi</t>
         </is>
       </c>
       <c r="H555" s="10" t="inlineStr">
         <is>
-          <t>Yusupova Dilnura Nuriddin qizi</t>
+          <t>Yusupova Asila Iskandar qizi</t>
         </is>
       </c>
       <c r="I555" s="9" t="inlineStr"/>
       <c r="J555" s="11" t="inlineStr">
         <is>
-          <t>AD9394045</t>
+          <t>AD0311873</t>
         </is>
       </c>
       <c r="K555" s="8" t="inlineStr">
         <is>
-          <t>60701085680029</t>
+          <t>61007015680048</t>
         </is>
       </c>
       <c r="L555" s="11" t="inlineStr">
         <is>
-          <t>13.11.2024</t>
+          <t>13.04.2021</t>
         </is>
       </c>
       <c r="M555" s="11" t="inlineStr">
         <is>
-          <t>07.01.2008</t>
+          <t>10.07.2001</t>
         </is>
       </c>
       <c r="N555" s="11" t="inlineStr">
@@ -52199,13 +52211,13 @@
       <c r="O555" s="10" t="inlineStr"/>
       <c r="P555" s="8" t="inlineStr">
         <is>
-          <t>UM 03274566</t>
+          <t>UM 0085864</t>
         </is>
       </c>
       <c r="Q555" s="10" t="inlineStr"/>
       <c r="R555" s="10" t="inlineStr">
         <is>
-          <t>44-maktab</t>
+          <t>51-maktab</t>
         </is>
       </c>
       <c r="S555" s="11" t="inlineStr">
@@ -52217,7 +52229,7 @@
       <c r="U555" s="11" t="inlineStr"/>
       <c r="V555" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
+          <t>2025-2026 kontingenti: 1-kurs, oldingi guruh 25-20</t>
         </is>
       </c>
       <c r="W555" s="6" t="inlineStr"/>
@@ -52233,67 +52245,67 @@
       </c>
       <c r="B556" s="2" t="inlineStr">
         <is>
-          <t>25-20</t>
+          <t>25-19</t>
         </is>
       </c>
       <c r="C556" s="3" t="inlineStr">
         <is>
-          <t>Yusupova Hosila</t>
+          <t>Yusupova Dilnura</t>
         </is>
       </c>
       <c r="D556" s="4" t="inlineStr"/>
       <c r="E556" s="5" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>98</t>
         </is>
       </c>
       <c r="F556" s="5" t="inlineStr"/>
       <c r="G556" s="5" t="inlineStr">
         <is>
-          <t>Akmal qizi</t>
+          <t>Nuriddin qizi</t>
         </is>
       </c>
       <c r="H556" s="4" t="inlineStr">
         <is>
-          <t>Yusupova Hosila Akmal qizi</t>
+          <t>Yusupova Dilnura Nuriddin qizi</t>
         </is>
       </c>
       <c r="I556" s="3" t="inlineStr"/>
       <c r="J556" s="5" t="inlineStr">
         <is>
-          <t>AD7115916</t>
+          <t>AD9394045</t>
         </is>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
-          <t>61205075590059</t>
+          <t>60701085680029</t>
         </is>
       </c>
       <c r="L556" s="5" t="inlineStr">
         <is>
-          <t>10.05.2024</t>
+          <t>13.11.2024</t>
         </is>
       </c>
       <c r="M556" s="5" t="inlineStr">
         <is>
-          <t>12.05.2007</t>
+          <t>07.01.2008</t>
         </is>
       </c>
       <c r="N556" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O556" s="4" t="inlineStr"/>
       <c r="P556" s="2" t="inlineStr">
         <is>
-          <t>UM 03295776</t>
+          <t>UM 03274566</t>
         </is>
       </c>
       <c r="Q556" s="4" t="inlineStr"/>
       <c r="R556" s="4" t="inlineStr">
         <is>
-          <t>7-maktab</t>
+          <t>44-maktab</t>
         </is>
       </c>
       <c r="S556" s="5" t="inlineStr">
@@ -52321,63 +52333,67 @@
       </c>
       <c r="B557" s="8" t="inlineStr">
         <is>
-          <t>24-15</t>
+          <t>25-20</t>
         </is>
       </c>
       <c r="C557" s="9" t="inlineStr">
         <is>
-          <t>Yusupova Oygul</t>
+          <t>Yusupova Hosila</t>
         </is>
       </c>
       <c r="D557" s="10" t="inlineStr"/>
       <c r="E557" s="11" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F557" s="11" t="inlineStr"/>
       <c r="G557" s="11" t="inlineStr">
         <is>
-          <t>Qurbonmurodovna</t>
+          <t>Akmal qizi</t>
         </is>
       </c>
       <c r="H557" s="10" t="inlineStr">
         <is>
-          <t>Yusupova Oygul Qurbonmurodovna</t>
+          <t>Yusupova Hosila Akmal qizi</t>
         </is>
       </c>
       <c r="I557" s="9" t="inlineStr"/>
       <c r="J557" s="11" t="inlineStr">
         <is>
-          <t>AD8393032</t>
+          <t>AD7115916</t>
         </is>
       </c>
       <c r="K557" s="8" t="inlineStr">
         <is>
-          <t>42211842700144</t>
+          <t>61205075590059</t>
         </is>
       </c>
       <c r="L557" s="11" t="inlineStr">
         <is>
-          <t>26.08.2024</t>
+          <t>10.05.2024</t>
         </is>
       </c>
       <c r="M557" s="11" t="inlineStr">
         <is>
-          <t>22.11.1984</t>
-        </is>
-      </c>
-      <c r="N557" s="11" t="inlineStr"/>
+          <t>12.05.2007</t>
+        </is>
+      </c>
+      <c r="N557" s="11" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
       <c r="O557" s="10" t="inlineStr"/>
       <c r="P557" s="8" t="inlineStr">
         <is>
-          <t>KHT 287013</t>
+          <t>UM 03295776</t>
         </is>
       </c>
       <c r="Q557" s="10" t="inlineStr"/>
       <c r="R557" s="10" t="inlineStr">
         <is>
-          <t>Chiroqchi tumanidagi kasb-hunar litseysi</t>
+          <t>7-maktab</t>
         </is>
       </c>
       <c r="S557" s="11" t="inlineStr">
@@ -52405,63 +52421,63 @@
       </c>
       <c r="B558" s="2" t="inlineStr">
         <is>
-          <t>25-19</t>
+          <t>24-15</t>
         </is>
       </c>
       <c r="C558" s="3" t="inlineStr">
         <is>
-          <t>Yusupova Shahnoza</t>
+          <t>Yusupova Oygul</t>
         </is>
       </c>
       <c r="D558" s="4" t="inlineStr"/>
-      <c r="E558" s="5" t="inlineStr"/>
+      <c r="E558" s="5" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
       <c r="F558" s="5" t="inlineStr"/>
       <c r="G558" s="5" t="inlineStr">
         <is>
-          <t>Akram qizi</t>
+          <t>Qurbonmurodovna</t>
         </is>
       </c>
       <c r="H558" s="4" t="inlineStr">
         <is>
-          <t>Yusupova Shahnoza Akram qizi</t>
+          <t>Yusupova Oygul Qurbonmurodovna</t>
         </is>
       </c>
       <c r="I558" s="3" t="inlineStr"/>
       <c r="J558" s="5" t="inlineStr">
         <is>
-          <t>AC2276486</t>
+          <t>AD8393032</t>
         </is>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
-          <t>61512025680035</t>
+          <t>42211842700144</t>
         </is>
       </c>
       <c r="L558" s="5" t="inlineStr">
         <is>
-          <t>13.10.2019</t>
+          <t>26.08.2024</t>
         </is>
       </c>
       <c r="M558" s="5" t="inlineStr">
         <is>
-          <t>15.12.2002</t>
-        </is>
-      </c>
-      <c r="N558" s="5" t="inlineStr">
-        <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
+          <t>22.11.1984</t>
+        </is>
+      </c>
+      <c r="N558" s="5" t="inlineStr"/>
       <c r="O558" s="4" t="inlineStr"/>
       <c r="P558" s="2" t="inlineStr">
         <is>
-          <t>UM 0420204</t>
+          <t>KHT 287013</t>
         </is>
       </c>
       <c r="Q558" s="4" t="inlineStr"/>
       <c r="R558" s="4" t="inlineStr">
         <is>
-          <t>63-maktab</t>
+          <t>Chiroqchi tumanidagi kasb-hunar litseysi</t>
         </is>
       </c>
       <c r="S558" s="5" t="inlineStr">
@@ -52489,62 +52505,46 @@
       </c>
       <c r="B559" s="8" t="inlineStr">
         <is>
-          <t>26-06</t>
+          <t>25-19</t>
         </is>
       </c>
       <c r="C559" s="9" t="inlineStr">
         <is>
-          <t>Zarifova Marjona</t>
-        </is>
-      </c>
-      <c r="D559" s="10" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E559" s="11" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="F559" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Yusupova Shahnoza</t>
+        </is>
+      </c>
+      <c r="D559" s="10" t="inlineStr"/>
+      <c r="E559" s="11" t="inlineStr"/>
+      <c r="F559" s="11" t="inlineStr"/>
       <c r="G559" s="11" t="inlineStr">
         <is>
-          <t>Samijon qizi</t>
+          <t>Akram qizi</t>
         </is>
       </c>
       <c r="H559" s="10" t="inlineStr">
         <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="I559" s="9" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
+          <t>Yusupova Shahnoza Akram qizi</t>
+        </is>
+      </c>
+      <c r="I559" s="9" t="inlineStr"/>
       <c r="J559" s="11" t="inlineStr">
         <is>
-          <t>AE4688777</t>
+          <t>AC2276486</t>
         </is>
       </c>
       <c r="K559" s="8" t="inlineStr">
         <is>
-          <t>63007085680074</t>
+          <t>61512025680035</t>
         </is>
       </c>
       <c r="L559" s="11" t="inlineStr">
         <is>
-          <t>20.10.2025</t>
+          <t>13.10.2019</t>
         </is>
       </c>
       <c r="M559" s="11" t="inlineStr">
         <is>
-          <t>30.07.2008</t>
+          <t>15.12.2002</t>
         </is>
       </c>
       <c r="N559" s="11" t="inlineStr">
@@ -52552,47 +52552,31 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O559" s="10" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
+      <c r="O559" s="10" t="inlineStr"/>
       <c r="P559" s="8" t="inlineStr">
         <is>
-          <t>UM 03729007</t>
-        </is>
-      </c>
-      <c r="Q559" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
-        </is>
-      </c>
+          <t>UM 0420204</t>
+        </is>
+      </c>
+      <c r="Q559" s="10" t="inlineStr"/>
       <c r="R559" s="10" t="inlineStr">
         <is>
-          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>63-maktab</t>
         </is>
       </c>
       <c r="S559" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T559" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U559" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V559" s="10" t="inlineStr"/>
-      <c r="W559" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T559" s="11" t="inlineStr"/>
+      <c r="U559" s="11" t="inlineStr"/>
+      <c r="V559" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W559" s="6" t="inlineStr"/>
       <c r="X559" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -52605,12 +52589,12 @@
       </c>
       <c r="B560" s="2" t="inlineStr">
         <is>
-          <t>25-17</t>
+          <t>26-06</t>
         </is>
       </c>
       <c r="C560" s="3" t="inlineStr">
         <is>
-          <t>Zaripova Setora</t>
+          <t>Zarifova Marjona</t>
         </is>
       </c>
       <c r="D560" s="4" t="inlineStr">
@@ -52620,66 +52604,82 @@
       </c>
       <c r="E560" s="5" t="inlineStr">
         <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="F560" s="5" t="inlineStr"/>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F560" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G560" s="5" t="inlineStr">
         <is>
-          <t>Zuxriddin qizi</t>
+          <t>Samijon qizi</t>
         </is>
       </c>
       <c r="H560" s="4" t="inlineStr">
         <is>
-          <t>Zaripova Setora Zuxriddin qizi</t>
-        </is>
-      </c>
-      <c r="I560" s="3" t="inlineStr"/>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
+      <c r="I560" s="3" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
       <c r="J560" s="5" t="inlineStr">
         <is>
-          <t>AD8594631</t>
+          <t>AE4688777</t>
         </is>
       </c>
       <c r="K560" s="2" t="inlineStr">
         <is>
-          <t>60609075730014</t>
+          <t>63007085680074</t>
         </is>
       </c>
       <c r="L560" s="5" t="inlineStr">
         <is>
-          <t>12.09.2024</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="M560" s="5" t="inlineStr">
         <is>
-          <t>06.09.2007</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="N560" s="5" t="inlineStr">
         <is>
-          <t>Yakkabog' tumani</t>
-        </is>
-      </c>
-      <c r="O560" s="4" t="inlineStr"/>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O560" s="4" t="inlineStr">
+        <is>
+          <t>Zarifova Marjona Samijon qizi</t>
+        </is>
+      </c>
       <c r="P560" s="2" t="inlineStr">
         <is>
-          <t>UM 03299021</t>
-        </is>
-      </c>
-      <c r="Q560" s="4" t="inlineStr"/>
+          <t>UM 03729007</t>
+        </is>
+      </c>
+      <c r="Q560" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3872465/3620476/81b023ef-f6b3-4528-9010-ad2d8ade7e99?preview=true</t>
+        </is>
+      </c>
       <c r="R560" s="4" t="inlineStr">
         <is>
-          <t>1-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>32-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="S560" s="5" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
+          <t>Shahodatnoma</t>
         </is>
       </c>
       <c r="T560" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="U560" s="7" t="inlineStr">
@@ -52687,12 +52687,12 @@
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V560" s="4" t="inlineStr">
-        <is>
-          <t>AI orqali tahlil qilinib qo'shildi</t>
-        </is>
-      </c>
-      <c r="W560" s="6" t="inlineStr"/>
+      <c r="V560" s="4" t="inlineStr"/>
+      <c r="W560" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
       <c r="X560" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -52705,63 +52705,71 @@
       </c>
       <c r="B561" s="8" t="inlineStr">
         <is>
-          <t>25-18</t>
+          <t>25-17</t>
         </is>
       </c>
       <c r="C561" s="9" t="inlineStr">
         <is>
-          <t>Zarqulova Komila</t>
-        </is>
-      </c>
-      <c r="D561" s="10" t="inlineStr"/>
-      <c r="E561" s="11" t="inlineStr"/>
+          <t>Zaripova Setora</t>
+        </is>
+      </c>
+      <c r="D561" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E561" s="11" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
       <c r="F561" s="11" t="inlineStr"/>
       <c r="G561" s="11" t="inlineStr">
         <is>
-          <t>Mirzayevna</t>
+          <t>Zuxriddin qizi</t>
         </is>
       </c>
       <c r="H561" s="10" t="inlineStr">
         <is>
-          <t>Zarqulova Komila Mirzayevna</t>
+          <t>Zaripova Setora Zuxriddin qizi</t>
         </is>
       </c>
       <c r="I561" s="9" t="inlineStr"/>
       <c r="J561" s="11" t="inlineStr">
         <is>
-          <t>AD9593473</t>
+          <t>AD8594631</t>
         </is>
       </c>
       <c r="K561" s="8" t="inlineStr">
         <is>
-          <t>63107085590134</t>
+          <t>60609075730014</t>
         </is>
       </c>
       <c r="L561" s="11" t="inlineStr">
         <is>
-          <t>27.11.2024</t>
+          <t>12.09.2024</t>
         </is>
       </c>
       <c r="M561" s="11" t="inlineStr">
         <is>
-          <t>31.07.2008</t>
+          <t>06.09.2007</t>
         </is>
       </c>
       <c r="N561" s="11" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabog' tumani</t>
         </is>
       </c>
       <c r="O561" s="10" t="inlineStr"/>
       <c r="P561" s="8" t="inlineStr">
         <is>
-          <t>UM 03300424</t>
+          <t>UM 03299021</t>
         </is>
       </c>
       <c r="Q561" s="10" t="inlineStr"/>
       <c r="R561" s="10" t="inlineStr">
         <is>
-          <t>43-maktab</t>
+          <t>1-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S561" s="11" t="inlineStr">
@@ -52769,11 +52777,19 @@
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T561" s="11" t="inlineStr"/>
-      <c r="U561" s="11" t="inlineStr"/>
+      <c r="T561" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U561" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
       <c r="V561" s="10" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: 2-kurs</t>
+          <t>AI orqali tahlil qilinib qo'shildi</t>
         </is>
       </c>
       <c r="W561" s="6" t="inlineStr"/>
@@ -52789,110 +52805,78 @@
       </c>
       <c r="B562" s="2" t="inlineStr">
         <is>
-          <t>26-04</t>
+          <t>25-18</t>
         </is>
       </c>
       <c r="C562" s="3" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda</t>
-        </is>
-      </c>
-      <c r="D562" s="4" t="inlineStr">
-        <is>
-          <t>To'lov qildi</t>
-        </is>
-      </c>
-      <c r="E562" s="5" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="F562" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+          <t>Zarqulova Komila</t>
+        </is>
+      </c>
+      <c r="D562" s="4" t="inlineStr"/>
+      <c r="E562" s="5" t="inlineStr"/>
+      <c r="F562" s="5" t="inlineStr"/>
       <c r="G562" s="5" t="inlineStr">
         <is>
-          <t>Sodiqovna</t>
+          <t>Mirzayevna</t>
         </is>
       </c>
       <c r="H562" s="4" t="inlineStr">
         <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
-      <c r="I562" s="3" t="inlineStr">
-        <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
+          <t>Zarqulova Komila Mirzayevna</t>
+        </is>
+      </c>
+      <c r="I562" s="3" t="inlineStr"/>
       <c r="J562" s="5" t="inlineStr">
         <is>
-          <t>AE5856503</t>
+          <t>AD9593473</t>
         </is>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
-          <t>63112085680039</t>
+          <t>63107085590134</t>
         </is>
       </c>
       <c r="L562" s="5" t="inlineStr">
         <is>
-          <t>14.01.2026</t>
+          <t>27.11.2024</t>
         </is>
       </c>
       <c r="M562" s="5" t="inlineStr">
         <is>
-          <t>31.12.2008</t>
+          <t>31.07.2008</t>
         </is>
       </c>
       <c r="N562" s="5" t="inlineStr">
         <is>
-          <t>Kitob tumani</t>
-        </is>
-      </c>
-      <c r="O562" s="4" t="inlineStr">
-        <is>
-          <t>Zayidova Shaboda Sodiqovna</t>
-        </is>
-      </c>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O562" s="4" t="inlineStr"/>
       <c r="P562" s="2" t="inlineStr">
         <is>
-          <t>UM 03729571</t>
-        </is>
-      </c>
-      <c r="Q562" s="4" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03300424</t>
+        </is>
+      </c>
+      <c r="Q562" s="4" t="inlineStr"/>
       <c r="R562" s="4" t="inlineStr">
         <is>
-          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
+          <t>43-maktab</t>
         </is>
       </c>
       <c r="S562" s="5" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T562" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="U562" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V562" s="4" t="inlineStr"/>
-      <c r="W562" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T562" s="5" t="inlineStr"/>
+      <c r="U562" s="5" t="inlineStr"/>
+      <c r="V562" s="4" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: 2-kurs</t>
+        </is>
+      </c>
+      <c r="W562" s="6" t="inlineStr"/>
       <c r="X562" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -52905,46 +52889,62 @@
       </c>
       <c r="B563" s="8" t="inlineStr">
         <is>
-          <t>24-13</t>
+          <t>26-04</t>
         </is>
       </c>
       <c r="C563" s="9" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Munisa</t>
-        </is>
-      </c>
-      <c r="D563" s="10" t="inlineStr"/>
-      <c r="E563" s="11" t="inlineStr"/>
-      <c r="F563" s="11" t="inlineStr"/>
+          <t>Zayidova Shaboda</t>
+        </is>
+      </c>
+      <c r="D563" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E563" s="11" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="F563" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
       <c r="G563" s="11" t="inlineStr">
         <is>
-          <t>Sherzod qizi</t>
+          <t>Sodiqovna</t>
         </is>
       </c>
       <c r="H563" s="10" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Munisa Sherzod qizi</t>
-        </is>
-      </c>
-      <c r="I563" s="9" t="inlineStr"/>
+          <t>Zayidova Shaboda Sodiqovna</t>
+        </is>
+      </c>
+      <c r="I563" s="9" t="inlineStr">
+        <is>
+          <t>Zayidova Shaboda Sodiqovna</t>
+        </is>
+      </c>
       <c r="J563" s="11" t="inlineStr">
         <is>
-          <t>AD4793465</t>
+          <t>AE5856503</t>
         </is>
       </c>
       <c r="K563" s="8" t="inlineStr">
         <is>
-          <t>60810065680099</t>
+          <t>63112085680039</t>
         </is>
       </c>
       <c r="L563" s="11" t="inlineStr">
         <is>
-          <t>06.10.2023</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="M563" s="11" t="inlineStr">
         <is>
-          <t>08.10.2006</t>
+          <t>31.12.2008</t>
         </is>
       </c>
       <c r="N563" s="11" t="inlineStr">
@@ -52952,31 +52952,47 @@
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O563" s="10" t="inlineStr"/>
+      <c r="O563" s="10" t="inlineStr">
+        <is>
+          <t>Zayidova Shaboda Sodiqovna</t>
+        </is>
+      </c>
       <c r="P563" s="8" t="inlineStr">
         <is>
-          <t>UM 02313341</t>
-        </is>
-      </c>
-      <c r="Q563" s="10" t="inlineStr"/>
+          <t>UM 03729571</t>
+        </is>
+      </c>
+      <c r="Q563" s="10" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/3996248/3512043/11e1a280-b336-4568-b8d4-10c0e4aec649?preview=true</t>
+        </is>
+      </c>
       <c r="R563" s="10" t="inlineStr">
         <is>
-          <t>266-sonli umumiy o'rta ta'lim maktabin</t>
+          <t>53-sonli umumiy o'rta ta'lim maktabini</t>
         </is>
       </c>
       <c r="S563" s="11" t="inlineStr">
         <is>
-          <t>Umumiy o'rta maktab</t>
-        </is>
-      </c>
-      <c r="T563" s="11" t="inlineStr"/>
-      <c r="U563" s="11" t="inlineStr"/>
-      <c r="V563" s="10" t="inlineStr">
-        <is>
-          <t>2025-2026 kontingenti: 3-kurs</t>
-        </is>
-      </c>
-      <c r="W563" s="6" t="inlineStr"/>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T563" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U563" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V563" s="10" t="inlineStr"/>
+      <c r="W563" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS</t>
+        </is>
+      </c>
       <c r="X563" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -52989,12 +53005,12 @@
       </c>
       <c r="B564" s="2" t="inlineStr">
         <is>
-          <t>Talabalar safidan chiqarilganlar</t>
+          <t>24-13</t>
         </is>
       </c>
       <c r="C564" s="3" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro</t>
+          <t>Ziyadullayeva Munisa</t>
         </is>
       </c>
       <c r="D564" s="4" t="inlineStr"/>
@@ -53002,46 +53018,50 @@
       <c r="F564" s="5" t="inlineStr"/>
       <c r="G564" s="5" t="inlineStr">
         <is>
-          <t>Ubaydullo qizi</t>
+          <t>Sherzod qizi</t>
         </is>
       </c>
       <c r="H564" s="4" t="inlineStr">
         <is>
-          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+          <t>Ziyadullayeva Munisa Sherzod qizi</t>
         </is>
       </c>
       <c r="I564" s="3" t="inlineStr"/>
       <c r="J564" s="5" t="inlineStr">
         <is>
-          <t>AD8888020</t>
+          <t>AD4793465</t>
         </is>
       </c>
       <c r="K564" s="2" t="inlineStr">
         <is>
-          <t>62609075590027</t>
+          <t>60810065680099</t>
         </is>
       </c>
       <c r="L564" s="5" t="inlineStr">
         <is>
-          <t>07,10,2024</t>
-        </is>
-      </c>
-      <c r="M564" s="5" t="inlineStr"/>
+          <t>06.10.2023</t>
+        </is>
+      </c>
+      <c r="M564" s="5" t="inlineStr">
+        <is>
+          <t>08.10.2006</t>
+        </is>
+      </c>
       <c r="N564" s="5" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani</t>
         </is>
       </c>
       <c r="O564" s="4" t="inlineStr"/>
       <c r="P564" s="2" t="inlineStr">
         <is>
-          <t>UM 03295463</t>
+          <t>UM 02313341</t>
         </is>
       </c>
       <c r="Q564" s="4" t="inlineStr"/>
       <c r="R564" s="4" t="inlineStr">
         <is>
-          <t>1-maktab</t>
+          <t>266-sonli umumiy o'rta ta'lim maktabin</t>
         </is>
       </c>
       <c r="S564" s="5" t="inlineStr">
@@ -53053,7 +53073,7 @@
       <c r="U564" s="5" t="inlineStr"/>
       <c r="V564" s="4" t="inlineStr">
         <is>
-          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+          <t>2025-2026 kontingenti: 3-kurs</t>
         </is>
       </c>
       <c r="W564" s="6" t="inlineStr"/>
@@ -53069,106 +53089,74 @@
       </c>
       <c r="B565" s="8" t="inlineStr">
         <is>
-          <t>26-01</t>
+          <t>Talabalar safidan chiqarilganlar</t>
         </is>
       </c>
       <c r="C565" s="9" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina</t>
+          <t>Ziyadullayeva Zahro</t>
         </is>
       </c>
       <c r="D565" s="10" t="inlineStr"/>
-      <c r="E565" s="11" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="F565" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-02 00:00:00</t>
-        </is>
-      </c>
+      <c r="E565" s="11" t="inlineStr"/>
+      <c r="F565" s="11" t="inlineStr"/>
       <c r="G565" s="11" t="inlineStr">
         <is>
-          <t>Alisher qizi</t>
+          <t>Ubaydullo qizi</t>
         </is>
       </c>
       <c r="H565" s="10" t="inlineStr">
         <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
-        </is>
-      </c>
-      <c r="I565" s="9" t="inlineStr">
-        <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
-        </is>
-      </c>
+          <t>Ziyadullayeva Zahro Ubaydullo qizi</t>
+        </is>
+      </c>
+      <c r="I565" s="9" t="inlineStr"/>
       <c r="J565" s="11" t="inlineStr">
         <is>
-          <t>AD9812146</t>
+          <t>AD8888020</t>
         </is>
       </c>
       <c r="K565" s="8" t="inlineStr">
         <is>
-          <t>61206075590076</t>
+          <t>62609075590027</t>
         </is>
       </c>
       <c r="L565" s="11" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
-        </is>
-      </c>
-      <c r="M565" s="11" t="inlineStr">
-        <is>
-          <t>12.06.2007</t>
-        </is>
-      </c>
+          <t>07,10,2024</t>
+        </is>
+      </c>
+      <c r="M565" s="11" t="inlineStr"/>
       <c r="N565" s="11" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O565" s="10" t="inlineStr">
-        <is>
-          <t>Ziyodullayeva Jasmina Alisher qizi</t>
-        </is>
-      </c>
+      <c r="O565" s="10" t="inlineStr"/>
       <c r="P565" s="8" t="inlineStr">
         <is>
-          <t>UM 03296188</t>
-        </is>
-      </c>
-      <c r="Q565" s="10" t="inlineStr">
-        <is>
-          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
-        </is>
-      </c>
+          <t>UM 03295463</t>
+        </is>
+      </c>
+      <c r="Q565" s="10" t="inlineStr"/>
       <c r="R565" s="10" t="inlineStr">
         <is>
-          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>1-maktab</t>
         </is>
       </c>
       <c r="S565" s="11" t="inlineStr">
         <is>
-          <t>Shahodatnoma</t>
-        </is>
-      </c>
-      <c r="T565" s="11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="U565" s="7" t="inlineStr">
-        <is>
-          <t>TOPILDI</t>
-        </is>
-      </c>
-      <c r="V565" s="10" t="inlineStr"/>
-      <c r="W565" s="13" t="inlineStr">
-        <is>
-          <t>Pasport: MOS | Shahodatnoma: MOS</t>
-        </is>
-      </c>
+          <t>Umumiy o'rta maktab</t>
+        </is>
+      </c>
+      <c r="T565" s="11" t="inlineStr"/>
+      <c r="U565" s="11" t="inlineStr"/>
+      <c r="V565" s="10" t="inlineStr">
+        <is>
+          <t>2025-2026 kontingenti: TSCH ro`yxati (guruhi ko`rsatilmagan)</t>
+        </is>
+      </c>
+      <c r="W565" s="6" t="inlineStr"/>
       <c r="X565" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
@@ -53181,86 +53169,198 @@
       </c>
       <c r="B566" s="2" t="inlineStr">
         <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C566" s="3" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina</t>
+        </is>
+      </c>
+      <c r="D566" s="4" t="inlineStr"/>
+      <c r="E566" s="5" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="F566" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="G566" s="5" t="inlineStr">
+        <is>
+          <t>Alisher qizi</t>
+        </is>
+      </c>
+      <c r="H566" s="4" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="I566" s="3" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="J566" s="5" t="inlineStr">
+        <is>
+          <t>AD9812146</t>
+        </is>
+      </c>
+      <c r="K566" s="2" t="inlineStr">
+        <is>
+          <t>61206075590076</t>
+        </is>
+      </c>
+      <c r="L566" s="5" t="inlineStr">
+        <is>
+          <t>13.12.2024</t>
+        </is>
+      </c>
+      <c r="M566" s="5" t="inlineStr">
+        <is>
+          <t>12.06.2007</t>
+        </is>
+      </c>
+      <c r="N566" s="5" t="inlineStr">
+        <is>
+          <t>Shahrisabz tumani</t>
+        </is>
+      </c>
+      <c r="O566" s="4" t="inlineStr">
+        <is>
+          <t>Ziyodullayeva Jasmina Alisher qizi</t>
+        </is>
+      </c>
+      <c r="P566" s="2" t="inlineStr">
+        <is>
+          <t>UM 03296188</t>
+        </is>
+      </c>
+      <c r="Q566" s="4" t="inlineStr">
+        <is>
+          <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
+        </is>
+      </c>
+      <c r="R566" s="4" t="inlineStr">
+        <is>
+          <t>14-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S566" s="5" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T566" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U566" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V566" s="4" t="inlineStr"/>
+      <c r="W566" s="13" t="inlineStr">
+        <is>
+          <t>Pasport: MOS | Shahodatnoma: MOS</t>
+        </is>
+      </c>
+      <c r="X566" s="7" t="inlineStr">
+        <is>
+          <t>TASDIQLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="22" customHeight="1">
+      <c r="A567" s="8" t="n">
+        <v>566</v>
+      </c>
+      <c r="B567" s="8" t="inlineStr">
+        <is>
           <t>25-17</t>
         </is>
       </c>
-      <c r="C566" s="3" t="inlineStr">
+      <c r="C567" s="9" t="inlineStr">
         <is>
           <t>Ziyodulloyeva Muxlisa</t>
         </is>
       </c>
-      <c r="D566" s="4" t="inlineStr"/>
-      <c r="E566" s="5" t="inlineStr"/>
-      <c r="F566" s="5" t="inlineStr"/>
-      <c r="G566" s="5" t="inlineStr">
+      <c r="D567" s="10" t="inlineStr"/>
+      <c r="E567" s="11" t="inlineStr"/>
+      <c r="F567" s="11" t="inlineStr"/>
+      <c r="G567" s="11" t="inlineStr">
         <is>
           <t>Shuhrat qizi</t>
         </is>
       </c>
-      <c r="H566" s="4" t="inlineStr">
+      <c r="H567" s="10" t="inlineStr">
         <is>
           <t>Ziyodulloyeva Muxlisa Shuhrat qizi</t>
         </is>
       </c>
-      <c r="I566" s="3" t="inlineStr"/>
-      <c r="J566" s="5" t="inlineStr">
+      <c r="I567" s="9" t="inlineStr"/>
+      <c r="J567" s="11" t="inlineStr">
         <is>
           <t>AD9345748</t>
         </is>
       </c>
-      <c r="K566" s="2" t="inlineStr">
+      <c r="K567" s="8" t="inlineStr">
         <is>
           <t>61504085680074</t>
         </is>
       </c>
-      <c r="L566" s="5" t="inlineStr">
+      <c r="L567" s="11" t="inlineStr">
         <is>
           <t>11.11.2024</t>
         </is>
       </c>
-      <c r="M566" s="5" t="inlineStr">
+      <c r="M567" s="11" t="inlineStr">
         <is>
           <t>15.04.2008</t>
         </is>
       </c>
-      <c r="N566" s="5" t="inlineStr">
+      <c r="N567" s="11" t="inlineStr">
         <is>
           <t>Kitob tumani</t>
         </is>
       </c>
-      <c r="O566" s="4" t="inlineStr"/>
-      <c r="P566" s="2" t="inlineStr">
+      <c r="O567" s="10" t="inlineStr"/>
+      <c r="P567" s="8" t="inlineStr">
         <is>
           <t>UM 03275067</t>
         </is>
       </c>
-      <c r="Q566" s="4" t="inlineStr"/>
-      <c r="R566" s="4" t="inlineStr">
+      <c r="Q567" s="10" t="inlineStr"/>
+      <c r="R567" s="10" t="inlineStr">
         <is>
           <t>61-maktab</t>
         </is>
       </c>
-      <c r="S566" s="5" t="inlineStr">
+      <c r="S567" s="11" t="inlineStr">
         <is>
           <t>Umumiy o'rta maktab</t>
         </is>
       </c>
-      <c r="T566" s="5" t="inlineStr"/>
-      <c r="U566" s="5" t="inlineStr"/>
-      <c r="V566" s="4" t="inlineStr">
+      <c r="T567" s="11" t="inlineStr"/>
+      <c r="U567" s="11" t="inlineStr"/>
+      <c r="V567" s="10" t="inlineStr">
         <is>
           <t>2025-2026 kontingenti: 2-kurs</t>
         </is>
       </c>
-      <c r="W566" s="6" t="inlineStr"/>
-      <c r="X566" s="7" t="inlineStr">
+      <c r="W567" s="6" t="inlineStr"/>
+      <c r="X567" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X566"/>
+  <autoFilter ref="A1:X567"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53271,7 +53371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -54913,109 +55013,209 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
+          <t>Xayrullayeva Asila</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>To'lov qildi</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Azamat qizi</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Xayrullayeva Asila Azamat qizi</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>AE6045063</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>62103095680022</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>26.01.2026</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>21.03.2009</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Kitob tumani</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="inlineStr">
+        <is>
+          <t>Mavjud</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>UM 03728305</t>
+        </is>
+      </c>
+      <c r="Q15" s="10" t="inlineStr"/>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>Kitob tumani 9-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>Shahodatnoma</t>
+        </is>
+      </c>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>TOPILDI</t>
+        </is>
+      </c>
+      <c r="V15" s="10" t="inlineStr"/>
+      <c r="W15" s="6" t="inlineStr"/>
+      <c r="X15" s="15" t="inlineStr">
+        <is>
+          <t>KUTILMOQDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>26-01</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
           <t>Ziyodullayeva Jasmina</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>233</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>2026-09-02 00:00:00</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Alisher qizi</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>AD9812146</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>61206075590076</t>
         </is>
       </c>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>13.12.2024</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>12.06.2007</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="O15" s="10" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>UM 03296188</t>
         </is>
       </c>
-      <c r="Q15" s="10" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>https://e-shahodatnoma.uz/api/public/getcertpdf/2973530/2550349/729447b3-f65c-4e5e-ae7d-8084bcb45e3b?preview=true</t>
         </is>
       </c>
-      <c r="R15" s="10" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>14-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="S16" s="5" t="inlineStr">
         <is>
           <t>Shahodatnoma</t>
         </is>
       </c>
-      <c r="T15" s="11" t="inlineStr">
+      <c r="T16" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="U15" s="7" t="inlineStr">
+      <c r="U16" s="7" t="inlineStr">
         <is>
           <t>TOPILDI</t>
         </is>
       </c>
-      <c r="V15" s="10" t="inlineStr"/>
-      <c r="W15" s="13" t="inlineStr">
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="13" t="inlineStr">
         <is>
           <t>Pasport: MOS | Shahodatnoma: MOS</t>
         </is>
       </c>
-      <c r="X15" s="7" t="inlineStr">
+      <c r="X16" s="7" t="inlineStr">
         <is>
           <t>TASDIQLANDI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X15"/>
+  <autoFilter ref="A1:X16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
